--- a/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J383"/>
+  <dimension ref="A1:J389"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1426,28 +1426,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>대표 시공 사진을 크게 쓴 히어로와 「우리 집은 얼마나 나올까요?」 견적 시작 버튼</v>
+        <v>끊어진 링크 — 갈 곳이 실제로 있는지</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈'에서 대표 시공 사진을 크게 쓴 히어로와 「우리 집은 얼마나 나올까요?」 견적 시작 버튼을 눌러 본다.</v>
+        <v>스펙팩 7-9-2 의 검사 글을 사이트 «뿌리»에서 한 번 돌린다. ⚠ pages/ 만 주면 한 층 위의 화면 목록을 못 봐서 멀쩡한 화면이 외톨이로 잘못 잡힌다.</v>
       </c>
       <c r="H20" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>끊어진 링크 0건. `href` 가 가리키는 .html 이 모두 실제로 있다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>평수 칩(10평대~40평대 이상)을 누르면 바뀌는 예상 비용 띠</v>
+        <v>없는 그림 · 빈 파일</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈' 화면에서 평수 칩(10평대~40평대 이상)을 누르면 바뀌는 예상 비용 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>같은 검사 글의 결과에서 «없는 그림»과 «빈 파일» 줄을 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>둘 다 0건. `src` 가 가리키는 파일이 모두 있고, 0바이트로 남은 화면이 없다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>시공 분야 6종 아이콘(아파트 전체·주방·욕실·상업공간·부분 시공·베란다)</v>
+        <v>외톨이 화면 — 아무 데서도 안 이어지는 화면</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면을 열고 시공 분야 6종 아이콘(아파트 전체·주방·욕실·상업공간·부분 시공·베란다)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>같은 검사 글의 «외톨이» 줄을 본다. 나온 화면은 어디서 이어져야 맞는지 정하고 그 링크를 놓는다.</v>
       </c>
       <c r="H22" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>외톨이 0건. 만들어 놓고 갈 길이 없는 화면이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>최근 시공 사례 6개 카드(비포·애프터 손잡이)</v>
+        <v>화면 수가 약속한 수와 같은지</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈' 화면을 열고 최근 시공 사례 6개 카드(비포·애프터 손잡이)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>만든 .html 수를 세어 스펙팩 4장의 화면 수와 견준다.</v>
       </c>
       <c r="H23" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>두 수가 같다. 목록에는 있는데 안 만든 화면, 만들었는데 목록에 없는 화면 둘 다 0.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>공사가 어떻게 굴러가는지 5단계 안내(상담→실측→계약→시공→준공)</v>
+        <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>'홈' 화면을 열고 공사가 어떻게 굴러가는지 5단계 안내(상담→실측→계약→시공→준공)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>우리 업체 숫자 3개(누적 현장 수·평균 공사 기간·하자보수 대응일)</v>
+        <v>굳은 날짜 — 견본 날짜가 오늘에서 거꾸로 잡혔는지</v>
       </c>
       <c r="G25" t="str">
-        <v>'홈' 화면을 열고 우리 업체 숫자 3개(누적 현장 수·평균 공사 기간·하자보수 대응일)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>목록·상세의 날짜와 요일을 오늘 기준으로 다시 센다. 요일은 눈으로 세지 말고 달력과 맞춘다.</v>
       </c>
       <c r="H25" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>지난 날짜가 「예정」으로 보이지 않는다. 요일이 그 날짜의 실제 요일과 같다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1621,25 +1621,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F26" t="str">
-        <v>자재</v>
+        <v>대표 시공 사진을 크게 쓴 히어로와 「우리 집은 얼마나 나올까요?」 견적 시작 버튼</v>
       </c>
       <c r="G26" t="str">
-        <v>'홈' 화면에서 자재가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 대표 시공 사진을 크게 쓴 히어로와 「우리 집은 얼마나 나올까요?」 견적 시작 버튼을 눌러 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1665,10 +1665,10 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>마감 브랜드 로고 띠</v>
+        <v>평수 칩(10평대~40평대 이상)을 누르면 바뀌는 예상 비용 띠</v>
       </c>
       <c r="G27" t="str">
-        <v>'홈' 화면에서 마감 브랜드 로고 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 평수 칩(10평대~40평대 이상)을 누르면 바뀌는 예상 비용 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H27" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1697,10 +1697,10 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>실제 고객 후기 4건</v>
+        <v>시공 분야 6종 아이콘(아파트 전체·주방·욕실·상업공간·부분 시공·베란다)</v>
       </c>
       <c r="G28" t="str">
-        <v>'홈' 화면을 열고 실제 고객 후기 4건이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면을 열고 시공 분야 6종 아이콘(아파트 전체·주방·욕실·상업공간·부분 시공·베란다)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H28" t="str">
         <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
@@ -1729,13 +1729,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>자주 묻는 질문 아코디언</v>
+        <v>최근 시공 사례 6개 카드(비포·애프터 손잡이)</v>
       </c>
       <c r="G29" t="str">
-        <v>'홈' 화면에서 자주 묻는 질문 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 최근 시공 사례 6개 카드(비포·애프터 손잡이)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H29" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1761,13 +1761,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>하단 상담 신청 CTA</v>
+        <v>공사가 어떻게 굴러가는지 5단계 안내(상담→실측→계약→시공→준공)</v>
       </c>
       <c r="G30" t="str">
-        <v>'홈'에서 하단 상담 신청 CTA을 눌러 본다.</v>
+        <v>'홈' 화면을 열고 공사가 어떻게 굴러가는지 5단계 안내(상담→실측→계약→시공→준공)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H30" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1778,28 +1778,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B31" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>시공 분야 홈</v>
+        <v/>
       </c>
       <c r="D31" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E31" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v>분야 대표 사진과 한 줄 소개(예: 욕실 시공)</v>
+        <v>우리 업체 숫자 3개(누적 현장 수·평균 공사 기간·하자보수 대응일)</v>
       </c>
       <c r="G31" t="str">
-        <v>'시공 분야 홈' 화면에서 분야 대표 사진과 한 줄 소개(예: 욕실 시공)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 우리 업체 숫자 3개(누적 현장 수·평균 공사 기간·하자보수 대응일)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>이 분야만의 공사 범위 탭(전체 교체·부분 보수)</v>
+        <v>자재</v>
       </c>
       <c r="G32" t="str">
-        <v>'시공 분야 홈'에서 이 분야만의 공사 범위 탭(전체 교체·부분 보수)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 자재가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H32" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>마감 등급 3단(기본·고급·프리미엄)별 평당 단가 표</v>
+        <v>마감 브랜드 로고 띠</v>
       </c>
       <c r="G33" t="str">
-        <v>'시공 분야 홈' 화면을 열고 마감 등급 3단(기본·고급·프리미엄)별 평당 단가 표가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 마감 브랜드 로고 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H33" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,10 +1889,10 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>이 분야 시공 사례 6개</v>
+        <v>실제 고객 후기 4건</v>
       </c>
       <c r="G34" t="str">
-        <v>'시공 분야 홈' 화면을 열고 이 분야 시공 사례 6개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면을 열고 실제 고객 후기 4건이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H34" t="str">
         <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -1921,13 +1921,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>이 분야에서 자주 놓치는 것 안내 카드(방수·배관 구배 등)</v>
+        <v>자주 묻는 질문 아코디언</v>
       </c>
       <c r="G35" t="str">
-        <v>'시공 분야 홈'의 이 분야에서 자주 놓치는 것 안내 카드(방수·배관 구배 등)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면에서 자주 묻는 질문 아코디언이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -1953,13 +1953,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>공정 순서와 걸리는 날수 표</v>
+        <v>하단 상담 신청 CTA</v>
       </c>
       <c r="G36" t="str">
-        <v>'시공 분야 홈' 화면에서 공정 순서와 걸리는 날수 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 하단 상담 신청 CTA을 눌러 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1973,25 +1973,25 @@
         <v>SCN-002</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>시공 분야 홈</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F37" t="str">
-        <v>이 분야 자주 묻는 질문 4개</v>
+        <v>분야 대표 사진과 한 줄 소개(예: 욕실 시공)</v>
       </c>
       <c r="G37" t="str">
-        <v>'시공 분야 홈' 화면을 열고 이 분야 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'시공 분야 홈' 화면에서 분야 대표 사진과 한 줄 소개(예: 욕실 시공)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H37" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>이 분야로 견적 시작 CTA</v>
+        <v>이 분야만의 공사 범위 탭(전체 교체·부분 보수)</v>
       </c>
       <c r="G38" t="str">
-        <v>'시공 분야 홈'에서 이 분야로 견적 시작 CTA을 눌러 본다.</v>
+        <v>'시공 분야 홈'에서 이 분야만의 공사 범위 탭(전체 교체·부분 보수)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2034,28 +2034,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B39" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>비용 안내</v>
+        <v/>
       </c>
       <c r="D39" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E39" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v>「값이 왜 이렇게 나오는지」를 먼저 밝히는 안내 화면</v>
+        <v>마감 등급 3단(기본·고급·프리미엄)별 평당 단가 표</v>
       </c>
       <c r="G39" t="str">
-        <v>'비용 안내' 화면에서 「값이 왜 이렇게 나오는지」를 먼저 밝히는 안내 화면이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공 분야 홈' 화면을 열고 마감 등급 3단(기본·고급·프리미엄)별 평당 단가 표가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H39" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -2081,13 +2081,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>평수와 공사 범위를 고르는 바</v>
+        <v>이 분야 시공 사례 6개</v>
       </c>
       <c r="G40" t="str">
-        <v>'비용 안내' 화면에서 평수와 공사 범위를 고르는 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공 분야 홈' 화면을 열고 이 분야 시공 사례 6개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H40" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -2113,13 +2113,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>총액 범위 막대(최소~최대)와 그 안에서 무엇이 값을 움직이는지</v>
+        <v>이 분야에서 자주 놓치는 것 안내 카드(방수·배관 구배 등)</v>
       </c>
       <c r="G41" t="str">
-        <v>'비용 안내' 화면에서 총액 범위 막대(최소~최대)와 그 안에서 무엇이 값을 움직이는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공 분야 홈'의 이 분야에서 자주 놓치는 것 안내 카드(방수·배관 구배 등)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B42" t="str">
         <v/>
@@ -2145,10 +2145,10 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>공정별 비용 비중 표(철거·설비·목공·타일·도배·마루·조명)</v>
+        <v>공정 순서와 걸리는 날수 표</v>
       </c>
       <c r="G42" t="str">
-        <v>'비용 안내' 화면에서 공정별 비용 비중 표(철거·설비·목공·타일·도배·마루·조명)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공 분야 홈' 화면에서 공정 순서와 걸리는 날수 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H42" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>마감 등급별 차이 비교 표</v>
+        <v>이 분야 자주 묻는 질문 4개</v>
       </c>
       <c r="G43" t="str">
-        <v>'비용 안내' 화면에서 마감 등급별 차이 비교 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공 분야 홈' 화면을 열고 이 분야 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>추가로 붙을 수 있는 비용 목록(폐기물·엘리베이터 사용료·야간 작업)</v>
+        <v>이 분야로 견적 시작 CTA</v>
       </c>
       <c r="G44" t="str">
-        <v>'비용 안내'의 추가로 붙을 수 있는 비용 목록(폐기물·엘리베이터 사용료·야간 작업)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'시공 분야 홈'에서 이 분야로 견적 시작 CTA을 눌러 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2229,22 +2229,22 @@
         <v>SCN-003</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>비용 안내</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>HO-03</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F45" t="str">
-        <v>계약금</v>
+        <v>「값이 왜 이렇게 나오는지」를 먼저 밝히는 안내 화면</v>
       </c>
       <c r="G45" t="str">
-        <v>'비용 안내' 화면에서 계약금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 「값이 왜 이렇게 나오는지」를 먼저 밝히는 안내 화면이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H45" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2273,10 +2273,10 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>중도금</v>
+        <v>평수와 공사 범위를 고르는 바</v>
       </c>
       <c r="G46" t="str">
-        <v>'비용 안내' 화면에서 중도금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 평수와 공사 범위를 고르는 바가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H46" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2305,10 +2305,10 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>잔금 분할 비율 안내</v>
+        <v>총액 범위 막대(최소~최대)와 그 안에서 무엇이 값을 움직이는지</v>
       </c>
       <c r="G47" t="str">
-        <v>'비용 안내' 화면에서 잔금 분할 비율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 총액 범위 막대(최소~최대)와 그 안에서 무엇이 값을 움직이는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H47" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2337,13 +2337,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>다른 업체와 견적을 견줄 때 볼 것 체크리스트</v>
+        <v>공정별 비용 비중 표(철거·설비·목공·타일·도배·마루·조명)</v>
       </c>
       <c r="G48" t="str">
-        <v>'비용 안내'의 다른 업체와 견적을 견줄 때 볼 것 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 공정별 비용 비중 표(철거·설비·목공·타일·도배·마루·조명)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H48" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2369,10 +2369,10 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>견적서 예시 내려받기</v>
+        <v>마감 등급별 차이 비교 표</v>
       </c>
       <c r="G49" t="str">
-        <v>'비용 안내' 화면에서 견적서 예시 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 마감 등급별 차이 비교 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H49" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2386,28 +2386,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B50" t="str">
-        <v>시공사례</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>시공사례 목록</v>
+        <v/>
       </c>
       <c r="D50" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>결과 수와 정렬(최신순·금액 낮은순·평수순)</v>
+        <v>추가로 붙을 수 있는 비용 목록(폐기물·엘리베이터 사용료·야간 작업)</v>
       </c>
       <c r="G50" t="str">
-        <v>'시공사례 목록'에서 결과 수와 정렬(최신순·금액 낮은순·평수순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'비용 안내'의 추가로 붙을 수 있는 비용 목록(폐기물·엘리베이터 사용료·야간 작업)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H50" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>필터 패널(평수 구간·시공 분야·예산 구간·스타일·지역)</v>
+        <v>계약금</v>
       </c>
       <c r="G51" t="str">
-        <v>'시공사례 목록'에서 필터 패널(평수 구간·시공 분야·예산 구간·스타일·지역)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'비용 안내' 화면에서 계약금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H51" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>사례 카드 격자(대표 사진·평수와 지역·공사 기간·총 금액대·스타일 꼬리표)</v>
+        <v>중도금</v>
       </c>
       <c r="G52" t="str">
-        <v>'시공사례 목록'의 사례 카드 격자(대표 사진·평수와 지역·공사 기간·총 금액대·스타일 꼬리표)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 중도금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H52" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -2497,13 +2497,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>카드 위 비포</v>
+        <v>잔금 분할 비율 안내</v>
       </c>
       <c r="G53" t="str">
-        <v>'시공사례 목록'의 카드 위 비포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 잔금 분할 비율 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H53" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>애프터 비교 손잡이</v>
+        <v>다른 업체와 견적을 견줄 때 볼 것 체크리스트</v>
       </c>
       <c r="G54" t="str">
-        <v>'시공사례 목록' 화면에서 애프터 비교 손잡이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내'의 다른 업체와 견적을 견줄 때 볼 것 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H54" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2546,7 +2546,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B55" t="str">
         <v/>
@@ -2561,10 +2561,10 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>고른 조건 칩 줄과 전체 지우기</v>
+        <v>견적서 예시 내려받기</v>
       </c>
       <c r="G55" t="str">
-        <v>'시공사례 목록' 화면에서 고른 조건 칩 줄과 전체 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비용 안내' 화면에서 견적서 예시 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H55" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2581,22 +2581,22 @@
         <v>SCN-004</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>시공사례</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>시공사례 목록</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F56" t="str">
-        <v>더 보기 페이지네이션</v>
+        <v>결과 수와 정렬(최신순·금액 낮은순·평수순)</v>
       </c>
       <c r="G56" t="str">
-        <v>'시공사례 목록'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'시공사례 목록'에서 결과 수와 정렬(최신순·금액 낮은순·평수순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H56" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -2625,13 +2625,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>조건에 맞는 것이 없을 때로 가는 길</v>
+        <v>필터 패널(평수 구간·시공 분야·예산 구간·스타일·지역)</v>
       </c>
       <c r="G57" t="str">
-        <v>'시공사례 목록' 화면에서 조건에 맞는 것이 없을 때로 가는 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록'에서 필터 패널(평수 구간·시공 분야·예산 구간·스타일·지역)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H57" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2642,28 +2642,28 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B58" t="str">
-        <v>시공사례</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>시공사례 상세</v>
+        <v/>
       </c>
       <c r="D58" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E58" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F58" t="str">
-        <v>현장 한 줄 소개(평수·지역·가족 구성·요구사항)</v>
+        <v>사례 카드 격자(대표 사진·평수와 지역·공사 기간·총 금액대·스타일 꼬리표)</v>
       </c>
       <c r="G58" t="str">
-        <v>'시공사례 상세' 화면에서 현장 한 줄 소개(평수·지역·가족 구성·요구사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록'의 사례 카드 격자(대표 사진·평수와 지역·공사 기간·총 금액대·스타일 꼬리표)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H58" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2689,13 +2689,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>공간 탭(거실·주방·욕실·침실·현관)</v>
+        <v>카드 위 비포</v>
       </c>
       <c r="G59" t="str">
-        <v>'시공사례 상세'에서 공간 탭(거실·주방·욕실·침실·현관)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'시공사례 목록'의 카드 위 비포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -2721,10 +2721,10 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>공간별 비포</v>
+        <v>애프터 비교 손잡이</v>
       </c>
       <c r="G60" t="str">
-        <v>'시공사례 상세' 화면에서 공간별 비포가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록' 화면에서 애프터 비교 손잡이가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H60" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B61" t="str">
         <v/>
@@ -2753,10 +2753,10 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>애프터 비교 사진과 사진 여러 장</v>
+        <v>고른 조건 칩 줄과 전체 지우기</v>
       </c>
       <c r="G61" t="str">
-        <v>'시공사례 상세' 화면에서 애프터 비교 사진과 사진 여러 장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록' 화면에서 고른 조건 칩 줄과 전체 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B62" t="str">
         <v/>
@@ -2785,13 +2785,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>이 현장에 쓴 자재 표(부위·제품명·색상·등급)</v>
+        <v>더 보기 페이지네이션</v>
       </c>
       <c r="G62" t="str">
-        <v>'시공사례 상세' 화면에서 이 현장에 쓴 자재 표(부위·제품명·색상·등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H62" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B63" t="str">
         <v/>
@@ -2817,10 +2817,10 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>실제 공정표와 걸린 날수</v>
+        <v>조건에 맞는 것이 없을 때로 가는 길</v>
       </c>
       <c r="G63" t="str">
-        <v>'시공사례 상세' 화면에서 실제 공정표와 걸린 날수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 목록' 화면에서 조건에 맞는 것이 없을 때로 가는 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2837,22 +2837,22 @@
         <v>SCN-005</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>시공사례</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>시공사례 상세</v>
       </c>
       <c r="D64" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F64" t="str">
-        <v>총 공사비와 공정별 비중</v>
+        <v>현장 한 줄 소개(평수·지역·가족 구성·요구사항)</v>
       </c>
       <c r="G64" t="str">
-        <v>'시공사례 상세' 화면에서 총 공사비와 공정별 비중이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 상세' 화면에서 현장 한 줄 소개(평수·지역·가족 구성·요구사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H64" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2881,13 +2881,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>집주인이 남긴 후기</v>
+        <v>공간 탭(거실·주방·욕실·침실·현관)</v>
       </c>
       <c r="G65" t="str">
-        <v>'시공사례 상세' 화면에서 집주인이 남긴 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 상세'에서 공간 탭(거실·주방·욕실·침실·현관)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H65" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2913,10 +2913,10 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>시공 중 생겼던 문제와 어떻게 풀었는지</v>
+        <v>공간별 비포</v>
       </c>
       <c r="G66" t="str">
-        <v>'시공사례 상세' 화면에서 시공 중 생겼던 문제와 어떻게 풀었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'시공사례 상세' 화면에서 공간별 비포가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H66" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>비슷한 사례 3개</v>
+        <v>애프터 비교 사진과 사진 여러 장</v>
       </c>
       <c r="G67" t="str">
-        <v>'시공사례 상세' 화면을 열고 비슷한 사례 3개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'시공사례 상세' 화면에서 애프터 비교 사진과 사진 여러 장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2977,13 +2977,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>「이 사례처럼 견적 내기」 버튼(조건이 채워진 채로 견적으로 간다)</v>
+        <v>이 현장에 쓴 자재 표(부위·제품명·색상·등급)</v>
       </c>
       <c r="G68" t="str">
-        <v>'시공사례 상세'에서 「이 사례처럼 견적 내기」 버튼(조건이 채워진 채로 견적으로 간다)를 눌러 본다.</v>
+        <v>'시공사례 상세' 화면에서 이 현장에 쓴 자재 표(부위·제품명·색상·등급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2994,28 +2994,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B69" t="str">
-        <v>시공사례</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>시공사례 - 결과 없음</v>
+        <v/>
       </c>
       <c r="D69" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E69" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v>고른 조건을 그대로 보여 주는 칩 줄과 「이 조건에 맞는 사례가 아직 없어요」 안내</v>
+        <v>실제 공정표와 걸린 날수</v>
       </c>
       <c r="G69" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 고른 조건을 그대로 보여 주는 칩 줄과 「이 조건에 맞는 사례가 아직 없어요」 안내가 보이는지 확인한다.</v>
+        <v>'시공사례 상세' 화면에서 실제 공정표와 걸린 날수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H69" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B70" t="str">
         <v/>
@@ -3041,13 +3041,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>어느 조건이 결과를 0으로 만들었는지 짚어 주는 문장</v>
+        <v>총 공사비와 공정별 비중</v>
       </c>
       <c r="G70" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 어느 조건이 결과를 0으로 만들었는지 짚어 주는 문장이 보이는지 확인한다.</v>
+        <v>'시공사례 상세' 화면에서 총 공사비와 공정별 비중이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B71" t="str">
         <v/>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>조건을 하나씩 지우는 버튼</v>
+        <v>집주인이 남긴 후기</v>
       </c>
       <c r="G71" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 조건을 하나씩 지우는 버튼이 보이는지 확인한다.</v>
+        <v>'시공사례 상세' 화면에서 집주인이 남긴 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B72" t="str">
         <v/>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>조건을 살짝 넓힌 추천 3개(예: 예산 구간 한 칸 넓히기)</v>
+        <v>시공 중 생겼던 문제와 어떻게 풀었는지</v>
       </c>
       <c r="G72" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 조건을 살짝 넓힌 추천 3개(예: 예산 구간 한 칸 넓히기)가 보이는지 확인한다.</v>
+        <v>'시공사례 상세' 화면에서 시공 중 생겼던 문제와 어떻게 풀었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H72" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B73" t="str">
         <v/>
@@ -3137,13 +3137,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>그래도 없으면 상담으로 가는 길</v>
+        <v>비슷한 사례 3개</v>
       </c>
       <c r="G73" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 그래도 없으면 상담으로 가는 길이 보이는지 확인한다.</v>
+        <v>'시공사례 상세' 화면을 열고 비슷한 사례 3개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H73" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B74" t="str">
         <v/>
@@ -3169,13 +3169,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>인기 사례 6개</v>
+        <v>「이 사례처럼 견적 내기」 버튼(조건이 채워진 채로 견적으로 간다)</v>
       </c>
       <c r="G74" t="str">
-        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 인기 사례 6개가 보이는지 확인한다.</v>
+        <v>'시공사례 상세'에서 「이 사례처럼 견적 내기」 버튼(조건이 채워진 채로 견적으로 간다)를 눌러 본다.</v>
       </c>
       <c r="H74" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3186,28 +3186,28 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B75" t="str">
         <v>시공사례</v>
       </c>
       <c r="C75" t="str">
-        <v>자재·마감 둘러보기</v>
+        <v>시공사례 - 결과 없음</v>
       </c>
       <c r="D75" t="str">
-        <v>CS-04</v>
+        <v>CS-03</v>
       </c>
       <c r="E75" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F75" t="str">
-        <v>부위 탭(바닥·벽·주방·욕실·창호)</v>
+        <v>고른 조건을 그대로 보여 주는 칩 줄과 「이 조건에 맞는 사례가 아직 없어요」 안내</v>
       </c>
       <c r="G75" t="str">
-        <v>'자재·마감 둘러보기'에서 부위 탭(바닥·벽·주방·욕실·창호)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 고른 조건을 그대로 보여 주는 칩 줄과 「이 조건에 맞는 사례가 아직 없어요」 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H75" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B76" t="str">
         <v/>
@@ -3233,13 +3233,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>자재 카드 격자(제품 사진·브랜드·등급·평당 추가금)</v>
+        <v>어느 조건이 결과를 0으로 만들었는지 짚어 주는 문장</v>
       </c>
       <c r="G76" t="str">
-        <v>'자재·마감 둘러보기'의 자재 카드 격자(제품 사진·브랜드·등급·평당 추가금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 어느 조건이 결과를 0으로 만들었는지 짚어 주는 문장이 보이는지 확인한다.</v>
       </c>
       <c r="H76" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B77" t="str">
         <v/>
@@ -3265,13 +3265,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>색상 견본 줄과 누르면 바뀌는 미리보기 사진</v>
+        <v>조건을 하나씩 지우는 버튼</v>
       </c>
       <c r="G77" t="str">
-        <v>'자재·마감 둘러보기' 화면에서 색상 견본 줄과 누르면 바뀌는 미리보기 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 조건을 하나씩 지우는 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H77" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -3297,13 +3297,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>등급 필터(기본 포함·추가금 있음)</v>
+        <v>조건을 살짝 넓힌 추천 3개(예: 예산 구간 한 칸 넓히기)</v>
       </c>
       <c r="G78" t="str">
-        <v>'자재·마감 둘러보기'에서 등급 필터(기본 포함·추가금 있음)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 조건을 살짝 넓힌 추천 3개(예: 예산 구간 한 칸 넓히기)가 보이는지 확인한다.</v>
       </c>
       <c r="H78" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B79" t="str">
         <v/>
@@ -3329,13 +3329,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>자재별 장단점과 관리법 짧은 글</v>
+        <v>그래도 없으면 상담으로 가는 길</v>
       </c>
       <c r="G79" t="str">
-        <v>'자재·마감 둘러보기' 화면에서 자재별 장단점과 관리법 짧은 글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 그래도 없으면 상담으로 가는 길이 보이는지 확인한다.</v>
       </c>
       <c r="H79" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B80" t="str">
         <v/>
@@ -3361,13 +3361,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>내가 고른 자재 담아두기 패널과 예상 추가금 합계</v>
+        <v>인기 사례 6개</v>
       </c>
       <c r="G80" t="str">
-        <v>'자재·마감 둘러보기'의 내가 고른 자재 담아두기 패널과 예상 추가금 합계가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '시공사례 - 결과 없음' 화면이 나오게 한 뒤, 인기 사례 6개가 보이는지 확인한다.</v>
       </c>
       <c r="H80" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3381,25 +3381,25 @@
         <v>SCN-007</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>시공사례</v>
       </c>
       <c r="C81" t="str">
-        <v/>
+        <v>자재·마감 둘러보기</v>
       </c>
       <c r="D81" t="str">
-        <v/>
+        <v>CS-04</v>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F81" t="str">
-        <v>「고른 자재로 견적 내기」 버튼</v>
+        <v>부위 탭(바닥·벽·주방·욕실·창호)</v>
       </c>
       <c r="G81" t="str">
-        <v>'자재·마감 둘러보기'에서 「고른 자재로 견적 내기」 버튼을 눌러 본다.</v>
+        <v>'자재·마감 둘러보기'에서 부위 탭(바닥·벽·주방·욕실·창호)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H81" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3410,28 +3410,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B82" t="str">
-        <v>견적</v>
+        <v/>
       </c>
       <c r="C82" t="str">
-        <v>견적 조건 입력 - 단계별</v>
+        <v/>
       </c>
       <c r="D82" t="str">
-        <v>ES-01</v>
+        <v/>
       </c>
       <c r="E82" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F82" t="str">
-        <v>한 번에 한 가지만 묻는 단계별 입력(6단계) — 한 화면 안에서 여섯 단계가 앞뒤로 오간다</v>
+        <v>자재 카드 격자(제품 사진·브랜드·등급·평당 추가금)</v>
       </c>
       <c r="G82" t="str">
-        <v>'견적 조건 입력 - 단계별'의 한 번에 한 가지만 묻는 단계별 입력(6단계) — 한 화면 안에서 여섯 단계가 앞뒤로 오간다에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'자재·마감 둘러보기'의 자재 카드 격자(제품 사진·브랜드·등급·평당 추가금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H82" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B83" t="str">
         <v/>
@@ -3457,13 +3457,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1단계 평수와 ㎡ 환산</v>
+        <v>색상 견본 줄과 누르면 바뀌는 미리보기 사진</v>
       </c>
       <c r="G83" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 1단계 평수와 ㎡ 환산이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'자재·마감 둘러보기' 화면에서 색상 견본 줄과 누르면 바뀌는 미리보기 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H83" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B84" t="str">
         <v/>
@@ -3489,13 +3489,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2단계 공사 범위(전체·부분)</v>
+        <v>등급 필터(기본 포함·추가금 있음)</v>
       </c>
       <c r="G84" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 2단계 공사 범위(전체·부분)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'자재·마감 둘러보기'에서 등급 필터(기본 포함·추가금 있음)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H84" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,13 +3521,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3단계 손볼 공간 체크(거실·주방·욕실·침실·베란다·현관)</v>
+        <v>자재별 장단점과 관리법 짧은 글</v>
       </c>
       <c r="G85" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 3단계 손볼 공간 체크(거실·주방·욕실·침실·베란다·현관)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'자재·마감 둘러보기' 화면에서 자재별 장단점과 관리법 짧은 글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H85" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>4단계 마감 등급 3단</v>
+        <v>내가 고른 자재 담아두기 패널과 예상 추가금 합계</v>
       </c>
       <c r="G86" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 4단계 마감 등급 3단이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'자재·마감 둘러보기'의 내가 고른 자재 담아두기 패널과 예상 추가금 합계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H86" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,13 +3585,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>5단계 거주 여부와 희망 착공 시기</v>
+        <v>「고른 자재로 견적 내기」 버튼</v>
       </c>
       <c r="G87" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 5단계 거주 여부와 희망 착공 시기가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'자재·마감 둘러보기'에서 「고른 자재로 견적 내기」 버튼을 눌러 본다.</v>
       </c>
       <c r="H87" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3605,25 +3605,25 @@
         <v>SCN-008</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>견적</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>견적 조건 입력 - 단계별</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>ES-01</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F88" t="str">
-        <v>6단계 연락처</v>
+        <v>한 번에 한 가지만 묻는 단계별 입력(6단계) — 한 화면 안에서 여섯 단계가 앞뒤로 오간다</v>
       </c>
       <c r="G88" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면을 열고 6단계 연락처가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'견적 조건 입력 - 단계별'의 한 번에 한 가지만 묻는 단계별 입력(6단계) — 한 화면 안에서 여섯 단계가 앞뒤로 오간다에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H88" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3649,13 +3649,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>위쪽 진행 막대는 «끝낸 만큼»만 찬다</v>
+        <v>1단계 평수와 ㎡ 환산</v>
       </c>
       <c r="G89" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면에서 위쪽 진행 막대는 «끝낸 만큼»만 찬다가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 1단계 평수와 ㎡ 환산이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H89" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>오른쪽에 실시간으로 오르내리는 예상 금액 미리보기</v>
+        <v>2단계 공사 범위(전체·부분)</v>
       </c>
       <c r="G90" t="str">
-        <v>'견적 조건 입력 - 단계별'의 오른쪽에 실시간으로 오르내리는 예상 금액 미리보기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 2단계 공사 범위(전체·부분)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H90" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3713,13 +3713,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>이전으로 돌아가도 답이 남는 것</v>
+        <v>3단계 손볼 공간 체크(거실·주방·욕실·침실·베란다·현관)</v>
       </c>
       <c r="G91" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면에서 이전으로 돌아가도 답이 남는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 3단계 손볼 공간 체크(거실·주방·욕실·침실·베란다·현관)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H91" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3745,13 +3745,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>「나중에 이어서 하기」 임시저장</v>
+        <v>4단계 마감 등급 3단</v>
       </c>
       <c r="G92" t="str">
-        <v>'견적 조건 입력 - 단계별' 화면에서 「나중에 이어서 하기」 임시저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 4단계 마감 등급 3단이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H92" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3762,28 +3762,28 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B93" t="str">
-        <v>견적</v>
+        <v/>
       </c>
       <c r="C93" t="str">
-        <v>견적 결과</v>
+        <v/>
       </c>
       <c r="D93" t="str">
-        <v>ES-02</v>
+        <v/>
       </c>
       <c r="E93" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F93" t="str">
-        <v>총액 범위를 큰 글자로(최소~최대)와 「실측 후 확정됩니다」 못 박는 안내</v>
+        <v>5단계 거주 여부와 희망 착공 시기</v>
       </c>
       <c r="G93" t="str">
-        <v>'견적 결과' 화면에서 총액 범위를 큰 글자로(최소~최대)와 「실측 후 확정됩니다」 못 박는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 5단계 거주 여부와 희망 착공 시기가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H93" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -3809,13 +3809,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>넣은 조건 요약 칩 줄과 고치기 버튼</v>
+        <v>6단계 연락처</v>
       </c>
       <c r="G94" t="str">
-        <v>'견적 결과'에서 넣은 조건 요약 칩 줄과 고치기 버튼을 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면을 열고 6단계 연락처가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H94" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>마감 등급 3단 전환 스위치(바꾸면 총액이 바로 바뀐다)</v>
+        <v>위쪽 진행 막대는 «끝낸 만큼»만 찬다</v>
       </c>
       <c r="G95" t="str">
-        <v>'견적 결과' 화면을 열고 마감 등급 3단 전환 스위치(바꾸면 총액이 바로 바뀐다)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면에서 위쪽 진행 막대는 «끝낸 만큼»만 찬다가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H95" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -3873,13 +3873,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>공정별 항목 표(공정·수량·단가·금액·켜고 끄기)</v>
+        <v>오른쪽에 실시간으로 오르내리는 예상 금액 미리보기</v>
       </c>
       <c r="G96" t="str">
-        <v>'견적 결과' 화면에서 공정별 항목 표(공정·수량·단가·금액·켜고 끄기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별'의 오른쪽에 실시간으로 오르내리는 예상 금액 미리보기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H96" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B97" t="str">
         <v/>
@@ -3905,10 +3905,10 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>항목을 펼치면 나오는 자재비</v>
+        <v>이전으로 돌아가도 답이 남는 것</v>
       </c>
       <c r="G97" t="str">
-        <v>'견적 결과' 화면에서 항목을 펼치면 나오는 자재비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면에서 이전으로 돌아가도 답이 남는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H97" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B98" t="str">
         <v/>
@@ -3937,10 +3937,10 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>인건비 갈래</v>
+        <v>「나중에 이어서 하기」 임시저장</v>
       </c>
       <c r="G98" t="str">
-        <v>'견적 결과' 화면에서 인건비 갈래가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 조건 입력 - 단계별' 화면에서 「나중에 이어서 하기」 임시저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3957,25 +3957,25 @@
         <v>SCN-009</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>견적</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>견적 결과</v>
       </c>
       <c r="D99" t="str">
-        <v/>
+        <v>ES-02</v>
       </c>
       <c r="E99" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F99" t="str">
-        <v>포함되지 않은 것 목록</v>
+        <v>총액 범위를 큰 글자로(최소~최대)와 「실측 후 확정됩니다」 못 박는 안내</v>
       </c>
       <c r="G99" t="str">
-        <v>'견적 결과'의 포함되지 않은 것 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 총액 범위를 큰 글자로(최소~최대)와 「실측 후 확정됩니다」 못 박는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -4001,13 +4001,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>돈 내는 차례(계약금·중도금·잔금) 미리보기</v>
+        <v>넣은 조건 요약 칩 줄과 고치기 버튼</v>
       </c>
       <c r="G100" t="str">
-        <v>'견적 결과' 화면에서 돈 내는 차례(계약금·중도금·잔금) 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과'에서 넣은 조건 요약 칩 줄과 고치기 버튼을 눌러 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4033,13 +4033,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>예상 공사 기간 막대</v>
+        <v>마감 등급 3단 전환 스위치(바꾸면 총액이 바로 바뀐다)</v>
       </c>
       <c r="G101" t="str">
-        <v>'견적 결과' 화면에서 예상 공사 기간 막대가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면을 열고 마감 등급 3단 전환 스위치(바꾸면 총액이 바로 바뀐다)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H101" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4065,10 +4065,10 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>「이 견적으로 실측 예약」과 「견적서 저장</v>
+        <v>공정별 항목 표(공정·수량·단가·금액·켜고 끄기)</v>
       </c>
       <c r="G102" t="str">
-        <v>'견적 결과' 화면에서 「이 견적으로 실측 예약」과 「견적서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 공정별 항목 표(공정·수량·단가·금액·켜고 끄기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4097,10 +4097,10 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>내려받기」</v>
+        <v>항목을 펼치면 나오는 자재비</v>
       </c>
       <c r="G103" t="str">
-        <v>'견적 결과' 화면에서 내려받기」가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 항목을 펼치면 나오는 자재비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H103" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4114,28 +4114,28 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B104" t="str">
-        <v>견적</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>견적 항목 상세</v>
+        <v/>
       </c>
       <c r="D104" t="str">
-        <v>ES-03</v>
+        <v/>
       </c>
       <c r="E104" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F104" t="str">
-        <v>공정 탭(철거·설비·전기·목공·타일·도배·마루·도장)</v>
+        <v>인건비 갈래</v>
       </c>
       <c r="G104" t="str">
-        <v>'견적 항목 상세'에서 공정 탭(철거·설비·전기·목공·타일·도배·마루·도장)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'견적 결과' 화면에서 인건비 갈래가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H104" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B105" t="str">
         <v/>
@@ -4161,13 +4161,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>공정별 세부 항목 표(품명·규격·수량·단위·단가·금액)</v>
+        <v>포함되지 않은 것 목록</v>
       </c>
       <c r="G105" t="str">
-        <v>'견적 항목 상세' 화면에서 공정별 세부 항목 표(품명·규격·수량·단위·단가·금액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과'의 포함되지 않은 것 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4193,10 +4193,10 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>자재 등급을 그 줄에서 바로 바꾸는 드롭다운</v>
+        <v>돈 내는 차례(계약금·중도금·잔금) 미리보기</v>
       </c>
       <c r="G106" t="str">
-        <v>'견적 항목 상세' 화면에서 자재 등급을 그 줄에서 바로 바꾸는 드롭다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 돈 내는 차례(계약금·중도금·잔금) 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H106" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -4225,10 +4225,10 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>수량을 직접 고치는 칸</v>
+        <v>예상 공사 기간 막대</v>
       </c>
       <c r="G107" t="str">
-        <v>'견적 항목 상세' 화면에서 수량을 직접 고치는 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 예상 공사 기간 막대가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H107" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B108" t="str">
         <v/>
@@ -4257,13 +4257,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>공정 합계와 전체 합계가 아래에 붙어 따라 오르는 것</v>
+        <v>「이 견적으로 실측 예약」과 「견적서 저장</v>
       </c>
       <c r="G108" t="str">
-        <v>'견적 항목 상세'의 공정 합계와 전체 합계가 아래에 붙어 따라 오르는 것이 실제 데이터와 같은지 대조한다.</v>
+        <v>'견적 결과' 화면에서 「이 견적으로 실측 예약」과 「견적서 저장이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H108" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -4289,10 +4289,10 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>이 공정에 걸리는 날수와 앞뒤 공정</v>
+        <v>내려받기」</v>
       </c>
       <c r="G109" t="str">
-        <v>'견적 항목 상세' 화면에서 이 공정에 걸리는 날수와 앞뒤 공정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 결과' 화면에서 내려받기」가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H109" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4309,25 +4309,25 @@
         <v>SCN-010</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>견적</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>견적 항목 상세</v>
       </c>
       <c r="D110" t="str">
-        <v/>
+        <v>ES-03</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F110" t="str">
-        <v>「왜 이 값인가」 설명 카드</v>
+        <v>공정 탭(철거·설비·전기·목공·타일·도배·마루·도장)</v>
       </c>
       <c r="G110" t="str">
-        <v>'견적 항목 상세'의 「왜 이 값인가」 설명 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'견적 항목 상세'에서 공정 탭(철거·설비·전기·목공·타일·도배·마루·도장)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H110" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4353,10 +4353,10 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>표 내려받기</v>
+        <v>공정별 세부 항목 표(품명·규격·수량·단위·단가·금액)</v>
       </c>
       <c r="G111" t="str">
-        <v>'견적 항목 상세' 화면에서 표 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 항목 상세' 화면에서 공정별 세부 항목 표(품명·규격·수량·단위·단가·금액)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H111" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4370,28 +4370,28 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B112" t="str">
-        <v>견적</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>견적 저장 완료</v>
+        <v/>
       </c>
       <c r="D112" t="str">
-        <v>ES-04</v>
+        <v/>
       </c>
       <c r="E112" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F112" t="str">
-        <v>저장됐다는 체크 표시와 견적 번호</v>
+        <v>자재 등급을 그 줄에서 바로 바꾸는 드롭다운</v>
       </c>
       <c r="G112" t="str">
-        <v>'견적 저장 완료'의 저장됐다는 체크 표시와 견적 번호가 실제 데이터와 같은지 대조한다.</v>
+        <v>'견적 항목 상세' 화면에서 자재 등급을 그 줄에서 바로 바꾸는 드롭다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H112" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>저장한 견적 요약 카드(조건·총액·유효기간)</v>
+        <v>수량을 직접 고치는 칸</v>
       </c>
       <c r="G113" t="str">
-        <v>'견적 저장 완료'의 저장한 견적 요약 카드(조건·총액·유효기간)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'견적 항목 상세' 화면에서 수량을 직접 고치는 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H113" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B114" t="str">
         <v/>
@@ -4449,13 +4449,13 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>견적서 이름 고치기</v>
+        <v>공정 합계와 전체 합계가 아래에 붙어 따라 오르는 것</v>
       </c>
       <c r="G114" t="str">
-        <v>'견적 저장 완료' 화면에서 견적서 이름 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 항목 상세'의 공정 합계와 전체 합계가 아래에 붙어 따라 오르는 것이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H114" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B115" t="str">
         <v/>
@@ -4481,10 +4481,10 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>PDF 내려받기</v>
+        <v>이 공정에 걸리는 날수와 앞뒤 공정</v>
       </c>
       <c r="G115" t="str">
-        <v>'견적 저장 완료' 화면에서 PDF 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 항목 상세' 화면에서 이 공정에 걸리는 날수와 앞뒤 공정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H115" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B116" t="str">
         <v/>
@@ -4513,13 +4513,13 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>문자로 받기</v>
+        <v>「왜 이 값인가」 설명 카드</v>
       </c>
       <c r="G116" t="str">
-        <v>'견적 저장 완료' 화면에서 문자로 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 항목 상세'의 「왜 이 값인가」 설명 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H116" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B117" t="str">
         <v/>
@@ -4545,13 +4545,13 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>링크 복사</v>
+        <v>표 내려받기</v>
       </c>
       <c r="G117" t="str">
-        <v>'견적 저장 완료'에서 링크 복사를 눌러 본다.</v>
+        <v>'견적 항목 상세' 화면에서 표 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H117" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4565,25 +4565,25 @@
         <v>SCN-011</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>견적</v>
       </c>
       <c r="C118" t="str">
-        <v/>
+        <v>견적 저장 완료</v>
       </c>
       <c r="D118" t="str">
-        <v/>
+        <v>ES-04</v>
       </c>
       <c r="E118" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F118" t="str">
-        <v>「이 견적은 30일 동안 유효해요」 안내와 값이 바뀔 수 있는 까닭</v>
+        <v>저장됐다는 체크 표시와 견적 번호</v>
       </c>
       <c r="G118" t="str">
-        <v>'견적 저장 완료' 화면에서 「이 견적은 30일 동안 유효해요」 안내와 값이 바뀔 수 있는 까닭이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 저장 완료'의 저장됐다는 체크 표시와 견적 번호가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H118" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4609,13 +4609,13 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>다음에 할 일 3개 카드(실측 예약·자재 고르기·사례 더 보기)</v>
+        <v>저장한 견적 요약 카드(조건·총액·유효기간)</v>
       </c>
       <c r="G119" t="str">
-        <v>'견적 저장 완료' 화면을 열고 다음에 할 일 3개 카드(실측 예약·자재 고르기·사례 더 보기)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'견적 저장 완료'의 저장한 견적 요약 카드(조건·총액·유효기간)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H119" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4641,13 +4641,13 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>내 견적 목록으로 가는 길</v>
+        <v>견적서 이름 고치기</v>
       </c>
       <c r="G120" t="str">
-        <v>'견적 저장 완료'의 내 견적 목록으로 가는 길을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'견적 저장 완료' 화면에서 견적서 이름 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H120" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4658,28 +4658,28 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B121" t="str">
-        <v>견적</v>
+        <v/>
       </c>
       <c r="C121" t="str">
-        <v>견적 견주기</v>
+        <v/>
       </c>
       <c r="D121" t="str">
-        <v>ES-05</v>
+        <v/>
       </c>
       <c r="E121" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F121" t="str">
-        <v>내가 저장한 견적 목록에서 두 개를 고르는 줄</v>
+        <v>PDF 내려받기</v>
       </c>
       <c r="G121" t="str">
-        <v>'견적 견주기'의 내가 저장한 견적 목록에서 두 개를 고르는 줄을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'견적 저장 완료' 화면에서 PDF 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H121" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B122" t="str">
         <v/>
@@ -4705,10 +4705,10 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>좌우로 나란히 놓인 두 견적 표</v>
+        <v>문자로 받기</v>
       </c>
       <c r="G122" t="str">
-        <v>'견적 견주기' 화면에서 좌우로 나란히 놓인 두 견적 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 저장 완료' 화면에서 문자로 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H122" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>다른 칸에 표시(색 배경)가 생기는 것</v>
+        <v>링크 복사</v>
       </c>
       <c r="G123" t="str">
-        <v>'견적 견주기'의 다른 칸에 표시(색 배경)가 생기는 것이 실제 데이터와 같은지 대조한다.</v>
+        <v>'견적 저장 완료'에서 링크 복사를 눌러 본다.</v>
       </c>
       <c r="H123" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B124" t="str">
         <v/>
@@ -4769,10 +4769,10 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>「다른 것만 보기」 토글</v>
+        <v>「이 견적은 30일 동안 유효해요」 안내와 값이 바뀔 수 있는 까닭</v>
       </c>
       <c r="G124" t="str">
-        <v>'견적 견주기' 화면에서 「다른 것만 보기」 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 저장 완료' 화면에서 「이 견적은 30일 동안 유효해요」 안내와 값이 바뀔 수 있는 까닭이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B125" t="str">
         <v/>
@@ -4801,13 +4801,13 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>총액 차이를 맨 위에 큰 글자로</v>
+        <v>다음에 할 일 3개 카드(실측 예약·자재 고르기·사례 더 보기)</v>
       </c>
       <c r="G125" t="str">
-        <v>'견적 견주기' 화면에서 총액 차이를 맨 위에 큰 글자로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 저장 완료' 화면을 열고 다음에 할 일 3개 카드(실측 예약·자재 고르기·사례 더 보기)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H125" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B126" t="str">
         <v/>
@@ -4833,13 +4833,13 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>공정별 금액 차이 막대</v>
+        <v>내 견적 목록으로 가는 길</v>
       </c>
       <c r="G126" t="str">
-        <v>'견적 견주기'의 공정별 금액 차이 막대가 실제 데이터와 같은지 대조한다.</v>
+        <v>'견적 저장 완료'의 내 견적 목록으로 가는 길을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H126" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4853,25 +4853,25 @@
         <v>SCN-012</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>견적</v>
       </c>
       <c r="C127" t="str">
-        <v/>
+        <v>견적 견주기</v>
       </c>
       <c r="D127" t="str">
-        <v/>
+        <v>ES-05</v>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F127" t="str">
-        <v>어느 쪽이 어떤 점에서 나은지 짚어 주는 한 줄</v>
+        <v>내가 저장한 견적 목록에서 두 개를 고르는 줄</v>
       </c>
       <c r="G127" t="str">
-        <v>'견적 견주기' 화면에서 어느 쪽이 어떤 점에서 나은지 짚어 주는 한 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기'의 내가 저장한 견적 목록에서 두 개를 고르는 줄을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H127" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4897,10 +4897,10 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>고른 견적으로 실측 예약하기</v>
+        <v>좌우로 나란히 놓인 두 견적 표</v>
       </c>
       <c r="G128" t="str">
-        <v>'견적 견주기' 화면에서 고른 견적으로 실측 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기' 화면에서 좌우로 나란히 놓인 두 견적 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H128" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4914,28 +4914,28 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B129" t="str">
-        <v>실측 예약</v>
+        <v/>
       </c>
       <c r="C129" t="str">
-        <v>방문 실측 예약</v>
+        <v/>
       </c>
       <c r="D129" t="str">
-        <v>VS-01</v>
+        <v/>
       </c>
       <c r="E129" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F129" t="str">
-        <v>가능한 날짜를 보여 주는 달력(꽉 찬 날은 흐리게, 오늘 이전은 안 눌림)</v>
+        <v>다른 칸에 표시(색 배경)가 생기는 것</v>
       </c>
       <c r="G129" t="str">
-        <v>'방문 실측 예약' 화면에서 가능한 날짜를 보여 주는 달력(꽉 찬 날은 흐리게, 오늘 이전은 안 눌림)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기'의 다른 칸에 표시(색 배경)가 생기는 것이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H129" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,10 +4961,10 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>고른 날의 시간대 칸(오전·오후 2시간 단위, 남은 자리 수 표시)</v>
+        <v>「다른 것만 보기」 토글</v>
       </c>
       <c r="G130" t="str">
-        <v>'방문 실측 예약' 화면에서 고른 날의 시간대 칸(오전·오후 2시간 단위, 남은 자리 수 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기' 화면에서 「다른 것만 보기」 토글이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H130" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B131" t="str">
         <v/>
@@ -4993,10 +4993,10 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>주소와 동</v>
+        <v>총액 차이를 맨 위에 큰 글자로</v>
       </c>
       <c r="G131" t="str">
-        <v>'방문 실측 예약' 화면에서 주소와 동이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기' 화면에서 총액 차이를 맨 위에 큰 글자로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H131" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B132" t="str">
         <v/>
@@ -5025,13 +5025,13 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>호수 입력</v>
+        <v>공정별 금액 차이 막대</v>
       </c>
       <c r="G132" t="str">
-        <v>'방문 실측 예약'의 호수 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'견적 견주기'의 공정별 금액 차이 막대가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H132" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B133" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>현장 상황 체크(거주 중·공실·짐 있음)</v>
+        <v>어느 쪽이 어떤 점에서 나은지 짚어 주는 한 줄</v>
       </c>
       <c r="G133" t="str">
-        <v>'방문 실측 예약' 화면에서 현장 상황 체크(거주 중·공실·짐 있음)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기' 화면에서 어느 쪽이 어떤 점에서 나은지 짚어 주는 한 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H133" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B134" t="str">
         <v/>
@@ -5089,10 +5089,10 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>실측에 걸리는 시간과 준비할 것 안내</v>
+        <v>고른 견적으로 실측 예약하기</v>
       </c>
       <c r="G134" t="str">
-        <v>'방문 실측 예약' 화면에서 실측에 걸리는 시간과 준비할 것 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 견주기' 화면에서 고른 견적으로 실측 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H134" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5109,25 +5109,25 @@
         <v>SCN-013</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>실측 예약</v>
       </c>
       <c r="C135" t="str">
-        <v/>
+        <v>방문 실측 예약</v>
       </c>
       <c r="D135" t="str">
-        <v/>
+        <v>VS-01</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F135" t="str">
-        <v>오른쪽 예약 요약 카드(날짜·시간·주소·담당)</v>
+        <v>가능한 날짜를 보여 주는 달력(꽉 찬 날은 흐리게, 오늘 이전은 안 눌림)</v>
       </c>
       <c r="G135" t="str">
-        <v>'방문 실측 예약'의 오른쪽 예약 요약 카드(날짜·시간·주소·담당)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'방문 실측 예약' 화면에서 가능한 날짜를 보여 주는 달력(꽉 찬 날은 흐리게, 오늘 이전은 안 눌림)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H135" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -5153,10 +5153,10 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>연결할 견적 고르기</v>
+        <v>고른 날의 시간대 칸(오전·오후 2시간 단위, 남은 자리 수 표시)</v>
       </c>
       <c r="G136" t="str">
-        <v>'방문 실측 예약' 화면에서 연결할 견적 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'방문 실측 예약' 화면에서 고른 날의 시간대 칸(오전·오후 2시간 단위, 남은 자리 수 표시)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H136" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>방문비 무료 안내와 취소 규정</v>
+        <v>주소와 동</v>
       </c>
       <c r="G137" t="str">
-        <v>'방문 실측 예약'에서 방문비 무료 안내와 취소 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'방문 실측 예약' 화면에서 주소와 동이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H137" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,28 +5202,28 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B138" t="str">
-        <v>실측 예약</v>
+        <v/>
       </c>
       <c r="C138" t="str">
-        <v>예약 내용 확인</v>
+        <v/>
       </c>
       <c r="D138" t="str">
-        <v>VS-02</v>
+        <v/>
       </c>
       <c r="E138" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F138" t="str">
-        <v>예약 내용을 한 장에 모아 보여 주는 확인 표(날짜·시간·주소·연락처·현장 상황·연결한 견적)</v>
+        <v>호수 입력</v>
       </c>
       <c r="G138" t="str">
-        <v>'예약 내용 확인' 화면에서 예약 내용을 한 장에 모아 보여 주는 확인 표(날짜·시간·주소·연락처·현장 상황·연결한 견적)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'방문 실측 예약'의 호수 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H138" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,13 +5249,13 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>줄마다 고치기 버튼</v>
+        <v>현장 상황 체크(거주 중·공실·짐 있음)</v>
       </c>
       <c r="G139" t="str">
-        <v>'예약 내용 확인'에서 줄마다 고치기 버튼을 눌러 본다.</v>
+        <v>'방문 실측 예약' 화면에서 현장 상황 체크(거주 중·공실·짐 있음)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H139" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,13 +5281,13 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>방문하는 담당자 카드(사진·이름·경력)</v>
+        <v>실측에 걸리는 시간과 준비할 것 안내</v>
       </c>
       <c r="G140" t="str">
-        <v>'예약 내용 확인'의 방문하는 담당자 카드(사진·이름·경력)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'방문 실측 예약' 화면에서 실측에 걸리는 시간과 준비할 것 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H140" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B141" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>실측 때 무엇을 하는지 3단계</v>
+        <v>오른쪽 예약 요약 카드(날짜·시간·주소·담당)</v>
       </c>
       <c r="G141" t="str">
-        <v>'예약 내용 확인' 화면을 열고 실측 때 무엇을 하는지 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'방문 실측 예약'의 오른쪽 예약 요약 카드(날짜·시간·주소·담당)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H141" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B142" t="str">
         <v/>
@@ -5345,13 +5345,13 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>준비해 주실 것 목록</v>
+        <v>연결할 견적 고르기</v>
       </c>
       <c r="G142" t="str">
-        <v>'예약 내용 확인'의 준비해 주실 것 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'방문 실측 예약' 화면에서 연결할 견적 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H142" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -5362,7 +5362,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B143" t="str">
         <v/>
@@ -5377,13 +5377,13 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>개인정보 수집 동의 체크(체크해야 확정 버튼이 열린다)</v>
+        <v>방문비 무료 안내와 취소 규정</v>
       </c>
       <c r="G143" t="str">
-        <v>'예약 내용 확인'의 개인정보 수집 동의 체크(체크해야 확정 버튼이 열린다)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'방문 실측 예약'에서 방문비 무료 안내와 취소 규정을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H143" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5397,25 +5397,25 @@
         <v>SCN-014</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>실측 예약</v>
       </c>
       <c r="C144" t="str">
-        <v/>
+        <v>예약 내용 확인</v>
       </c>
       <c r="D144" t="str">
-        <v/>
+        <v>VS-02</v>
       </c>
       <c r="E144" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F144" t="str">
-        <v>취소</v>
+        <v>예약 내용을 한 장에 모아 보여 주는 확인 표(날짜·시간·주소·연락처·현장 상황·연결한 견적)</v>
       </c>
       <c r="G144" t="str">
-        <v>'예약 내용 확인'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 내용 확인' 화면에서 예약 내용을 한 장에 모아 보여 주는 확인 표(날짜·시간·주소·연락처·현장 상황·연결한 견적)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H144" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5441,13 +5441,13 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>변경 규정</v>
+        <v>줄마다 고치기 버튼</v>
       </c>
       <c r="G145" t="str">
-        <v>'예약 내용 확인' 화면에서 변경 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내용 확인'에서 줄마다 고치기 버튼을 눌러 본다.</v>
       </c>
       <c r="H145" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5473,13 +5473,13 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>예약 확정 버튼</v>
+        <v>방문하는 담당자 카드(사진·이름·경력)</v>
       </c>
       <c r="G146" t="str">
-        <v>'예약 내용 확인'에서 예약 확정 버튼을 눌러 본다.</v>
+        <v>'예약 내용 확인'의 방문하는 담당자 카드(사진·이름·경력)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5490,28 +5490,28 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B147" t="str">
-        <v>실측 예약</v>
+        <v/>
       </c>
       <c r="C147" t="str">
-        <v>예약 완료</v>
+        <v/>
       </c>
       <c r="D147" t="str">
-        <v>VS-03</v>
+        <v/>
       </c>
       <c r="E147" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F147" t="str">
-        <v>예약됐다는 체크 표시와 예약 번호</v>
+        <v>실측 때 무엇을 하는지 3단계</v>
       </c>
       <c r="G147" t="str">
-        <v>'예약 완료'의 예약됐다는 체크 표시와 예약 번호가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 내용 확인' 화면을 열고 실측 때 무엇을 하는지 3단계가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H147" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>날짜</v>
+        <v>준비해 주실 것 목록</v>
       </c>
       <c r="G148" t="str">
-        <v>'예약 완료' 화면에서 날짜가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내용 확인'의 준비해 주실 것 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H148" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -5569,13 +5569,13 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>시간을 큰 글자로</v>
+        <v>개인정보 수집 동의 체크(체크해야 확정 버튼이 열린다)</v>
       </c>
       <c r="G149" t="str">
-        <v>'예약 완료' 화면에서 시간을 큰 글자로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내용 확인'의 개인정보 수집 동의 체크(체크해야 확정 버튼이 열린다)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H149" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -5601,13 +5601,13 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>담당자 연락처와 문자 안내</v>
+        <v>취소</v>
       </c>
       <c r="G150" t="str">
-        <v>'예약 완료' 화면에서 담당자 연락처와 문자 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내용 확인'에서 취소를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H150" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -5633,13 +5633,13 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>내 캘린더에 담기 버튼</v>
+        <v>변경 규정</v>
       </c>
       <c r="G151" t="str">
-        <v>'예약 완료'에서 내 캘린더에 담기 버튼을 눌러 본다.</v>
+        <v>'예약 내용 확인' 화면에서 변경 규정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H151" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>실측 전날 알림이 간다는 안내</v>
+        <v>예약 확정 버튼</v>
       </c>
       <c r="G152" t="str">
-        <v>'예약 완료' 화면에서 실측 전날 알림이 간다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 내용 확인'에서 예약 확정 버튼을 눌러 본다.</v>
       </c>
       <c r="H152" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5685,25 +5685,25 @@
         <v>SCN-015</v>
       </c>
       <c r="B153" t="str">
-        <v/>
+        <v>실측 예약</v>
       </c>
       <c r="C153" t="str">
-        <v/>
+        <v>예약 완료</v>
       </c>
       <c r="D153" t="str">
-        <v/>
+        <v>VS-03</v>
       </c>
       <c r="E153" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F153" t="str">
-        <v>실측 뒤 무엇이 이어지는지 3단계(확정 견적→계약→착공)</v>
+        <v>예약됐다는 체크 표시와 예약 번호</v>
       </c>
       <c r="G153" t="str">
-        <v>'예약 완료' 화면을 열고 실측 뒤 무엇이 이어지는지 3단계(확정 견적→계약→착공)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'예약 완료'의 예약됐다는 체크 표시와 예약 번호가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H153" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5729,10 +5729,10 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>예약 변경</v>
+        <v>날짜</v>
       </c>
       <c r="G154" t="str">
-        <v>'예약 완료' 화면에서 예약 변경이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 완료' 화면에서 날짜가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H154" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5761,13 +5761,13 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>취소로 가는 길</v>
+        <v>시간을 큰 글자로</v>
       </c>
       <c r="G155" t="str">
-        <v>'예약 완료'에서 취소로 가는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 완료' 화면에서 시간을 큰 글자로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H155" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -5793,10 +5793,10 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>기다리는 동안 볼 것(사례·자재)</v>
+        <v>담당자 연락처와 문자 안내</v>
       </c>
       <c r="G156" t="str">
-        <v>'예약 완료' 화면에서 기다리는 동안 볼 것(사례·자재)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 완료' 화면에서 담당자 연락처와 문자 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H156" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5810,28 +5810,28 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B157" t="str">
-        <v>실측 예약</v>
+        <v/>
       </c>
       <c r="C157" t="str">
-        <v>예약 변경·취소</v>
+        <v/>
       </c>
       <c r="D157" t="str">
-        <v>VS-04</v>
+        <v/>
       </c>
       <c r="E157" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F157" t="str">
-        <v>지금 잡힌 예약 요약 카드</v>
+        <v>내 캘린더에 담기 버튼</v>
       </c>
       <c r="G157" t="str">
-        <v>'예약 변경·취소'의 지금 잡힌 예약 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'예약 완료'에서 내 캘린더에 담기 버튼을 눌러 본다.</v>
       </c>
       <c r="H157" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -5857,13 +5857,13 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>「날짜만 바꾸기」와 「아예 취소하기」 두 갈래</v>
+        <v>실측 전날 알림이 간다는 안내</v>
       </c>
       <c r="G158" t="str">
-        <v>'예약 변경·취소'에서 「날짜만 바꾸기」와 「아예 취소하기」 두 갈래를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 완료' 화면에서 실측 전날 알림이 간다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H158" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -5889,13 +5889,13 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>날짜 바꾸기를 고르면 펼쳐지는 달력과 남은 자리</v>
+        <v>실측 뒤 무엇이 이어지는지 3단계(확정 견적→계약→착공)</v>
       </c>
       <c r="G159" t="str">
-        <v>'예약 변경·취소'의 날짜 바꾸기를 고르면 펼쳐지는 달력과 남은 자리가 실제 데이터와 같은지 대조한다.</v>
+        <v>'예약 완료' 화면을 열고 실측 뒤 무엇이 이어지는지 3단계(확정 견적→계약→착공)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H159" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -5921,13 +5921,13 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>취소를 고르면 나오는 사유 선택과 자유 입력</v>
+        <v>예약 변경</v>
       </c>
       <c r="G160" t="str">
-        <v>'예약 변경·취소'에서 취소를 고르면 나오는 사유 선택과 자유 입력을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'예약 완료' 화면에서 예약 변경이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H160" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>하루 전까지는 그냥 되고 당일에는 연락이 필요하다는 안내</v>
+        <v>취소로 가는 길</v>
       </c>
       <c r="G161" t="str">
-        <v>'예약 변경·취소' 화면에서 하루 전까지는 그냥 되고 당일에는 연락이 필요하다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 완료'에서 취소로 가는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H161" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -5985,10 +5985,10 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>바뀐 내용 미리보기</v>
+        <v>기다리는 동안 볼 것(사례·자재)</v>
       </c>
       <c r="G162" t="str">
-        <v>'예약 변경·취소' 화면에서 바뀐 내용 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 완료' 화면에서 기다리는 동안 볼 것(사례·자재)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H162" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6005,25 +6005,25 @@
         <v>SCN-016</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>실측 예약</v>
       </c>
       <c r="C163" t="str">
-        <v/>
+        <v>예약 변경·취소</v>
       </c>
       <c r="D163" t="str">
-        <v/>
+        <v>VS-04</v>
       </c>
       <c r="E163" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F163" t="str">
-        <v>확정 버튼(되돌릴 수 없다는 확인)</v>
+        <v>지금 잡힌 예약 요약 카드</v>
       </c>
       <c r="G163" t="str">
-        <v>'예약 변경·취소'에서 확정 버튼(되돌릴 수 없다는 확인)을 눌러 본다.</v>
+        <v>'예약 변경·취소'의 지금 잡힌 예약 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H163" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6034,28 +6034,28 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B164" t="str">
-        <v>계약·결제</v>
+        <v/>
       </c>
       <c r="C164" t="str">
-        <v>계약서 확인·서명</v>
+        <v/>
       </c>
       <c r="D164" t="str">
-        <v>CT-01</v>
+        <v/>
       </c>
       <c r="E164" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F164" t="str">
-        <v>실측으로 확정된 견적과 처음 견적의 차이를 맨 위에 밝히는 표</v>
+        <v>「날짜만 바꾸기」와 「아예 취소하기」 두 갈래</v>
       </c>
       <c r="G164" t="str">
-        <v>'계약서 확인·서명' 화면에서 실측으로 확정된 견적과 처음 견적의 차이를 맨 위에 밝히는 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 변경·취소'에서 「날짜만 바꾸기」와 「아예 취소하기」 두 갈래를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H164" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,13 +6081,13 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>계약서 조항 목록(공사 범위·기간·금액·지급 시기·지체상금·하자보수·해지)</v>
+        <v>날짜 바꾸기를 고르면 펼쳐지는 달력과 남은 자리</v>
       </c>
       <c r="G165" t="str">
-        <v>'계약서 확인·서명'의 계약서 조항 목록(공사 범위·기간·금액·지급 시기·지체상금·하자보수·해지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'예약 변경·취소'의 날짜 바꾸기를 고르면 펼쳐지는 달력과 남은 자리가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H165" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B166" t="str">
         <v/>
@@ -6113,13 +6113,13 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>조항마다 펼쳐 보는 전문과 「쉽게 말하면」 한 줄</v>
+        <v>취소를 고르면 나오는 사유 선택과 자유 입력</v>
       </c>
       <c r="G166" t="str">
-        <v>'계약서 확인·서명' 화면에서 조항마다 펼쳐 보는 전문과 「쉽게 말하면」 한 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 변경·취소'에서 취소를 고르면 나오는 사유 선택과 자유 입력을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H166" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6130,7 +6130,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B167" t="str">
         <v/>
@@ -6145,13 +6145,13 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>첨부 도면과 자재 목록</v>
+        <v>하루 전까지는 그냥 되고 당일에는 연락이 필요하다는 안내</v>
       </c>
       <c r="G167" t="str">
-        <v>'계약서 확인·서명'의 첨부 도면과 자재 목록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'예약 변경·취소' 화면에서 하루 전까지는 그냥 되고 당일에는 연락이 필요하다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H167" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B168" t="str">
         <v/>
@@ -6177,10 +6177,10 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>손으로 그리는 서명란과 지우기</v>
+        <v>바뀐 내용 미리보기</v>
       </c>
       <c r="G168" t="str">
-        <v>'계약서 확인·서명' 화면에서 손으로 그리는 서명란과 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'예약 변경·취소' 화면에서 바뀐 내용 미리보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H168" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>동의 체크 3개(계약 조건·개인정보·전자서명)</v>
+        <v>확정 버튼(되돌릴 수 없다는 확인)</v>
       </c>
       <c r="G169" t="str">
-        <v>'계약서 확인·서명' 화면을 열고 동의 체크 3개(계약 조건·개인정보·전자서명)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'예약 변경·취소'에서 확정 버튼(되돌릴 수 없다는 확인)을 눌러 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6229,25 +6229,25 @@
         <v>SCN-017</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>계약·결제</v>
       </c>
       <c r="C170" t="str">
-        <v/>
+        <v>계약서 확인·서명</v>
       </c>
       <c r="D170" t="str">
-        <v/>
+        <v>CT-01</v>
       </c>
       <c r="E170" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F170" t="str">
-        <v>셋을 다 해야 열리는 계약 버튼</v>
+        <v>실측으로 확정된 견적과 처음 견적의 차이를 맨 위에 밝히는 표</v>
       </c>
       <c r="G170" t="str">
-        <v>'계약서 확인·서명'에서 셋을 다 해야 열리는 계약 버튼을 눌러 본다.</v>
+        <v>'계약서 확인·서명' 화면에서 실측으로 확정된 견적과 처음 견적의 차이를 맨 위에 밝히는 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -6273,13 +6273,13 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>계약서 PDF 내려받기</v>
+        <v>계약서 조항 목록(공사 범위·기간·금액·지급 시기·지체상금·하자보수·해지)</v>
       </c>
       <c r="G171" t="str">
-        <v>'계약서 확인·서명' 화면에서 계약서 PDF 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약서 확인·서명'의 계약서 조항 목록(공사 범위·기간·금액·지급 시기·지체상금·하자보수·해지)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H171" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6290,28 +6290,28 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B172" t="str">
-        <v>계약·결제</v>
+        <v/>
       </c>
       <c r="C172" t="str">
-        <v>계약금 결제</v>
+        <v/>
       </c>
       <c r="D172" t="str">
-        <v>CT-02</v>
+        <v/>
       </c>
       <c r="E172" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F172" t="str">
-        <v>이번에 낼 금액을 큰 글자로와 전체 대금 중 몇 번째인지 단계 막대</v>
+        <v>조항마다 펼쳐 보는 전문과 「쉽게 말하면」 한 줄</v>
       </c>
       <c r="G172" t="str">
-        <v>'계약금 결제'의 이번에 낼 금액을 큰 글자로와 전체 대금 중 몇 번째인지 단계 막대가 실제 데이터와 같은지 대조한다.</v>
+        <v>'계약서 확인·서명' 화면에서 조항마다 펼쳐 보는 전문과 「쉽게 말하면」 한 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H172" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B173" t="str">
         <v/>
@@ -6337,13 +6337,13 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>결제 수단 탭(카드·계좌이체·무통장)</v>
+        <v>첨부 도면과 자재 목록</v>
       </c>
       <c r="G173" t="str">
-        <v>'계약금 결제'에서 결제 수단 탭(카드·계좌이체·무통장)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'계약서 확인·서명'의 첨부 도면과 자재 목록에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H173" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B174" t="str">
         <v/>
@@ -6369,13 +6369,13 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>수단별 입력칸</v>
+        <v>손으로 그리는 서명란과 지우기</v>
       </c>
       <c r="G174" t="str">
-        <v>'계약금 결제'의 수단별 입력칸에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'계약서 확인·서명' 화면에서 손으로 그리는 서명란과 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -6401,13 +6401,13 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>할부 개월과 월 납입액 계산</v>
+        <v>동의 체크 3개(계약 조건·개인정보·전자서명)</v>
       </c>
       <c r="G175" t="str">
-        <v>'계약금 결제' 화면에서 할부 개월과 월 납입액 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약서 확인·서명' 화면을 열고 동의 체크 3개(계약 조건·개인정보·전자서명)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,13 +6433,13 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>현금영수증</v>
+        <v>셋을 다 해야 열리는 계약 버튼</v>
       </c>
       <c r="G176" t="str">
-        <v>'계약금 결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약서 확인·서명'에서 셋을 다 해야 열리는 계약 버튼을 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,13 +6465,13 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>세금계산서 발급 정보</v>
+        <v>계약서 PDF 내려받기</v>
       </c>
       <c r="G177" t="str">
-        <v>'계약금 결제'의 세금계산서 발급 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'계약서 확인·서명' 화면에서 계약서 PDF 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -6485,25 +6485,25 @@
         <v>SCN-018</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>계약·결제</v>
       </c>
       <c r="C178" t="str">
-        <v/>
+        <v>계약금 결제</v>
       </c>
       <c r="D178" t="str">
-        <v/>
+        <v>CT-02</v>
       </c>
       <c r="E178" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F178" t="str">
-        <v>결제 전 마지막 확인 요약(현장·금액·다음 낼 날)</v>
+        <v>이번에 낼 금액을 큰 글자로와 전체 대금 중 몇 번째인지 단계 막대</v>
       </c>
       <c r="G178" t="str">
-        <v>'계약금 결제'에서 결제 전 마지막 확인 요약(현장·금액·다음 낼 날)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'계약금 결제'의 이번에 낼 금액을 큰 글자로와 전체 대금 중 몇 번째인지 단계 막대가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H178" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6529,13 +6529,13 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>안전거래 안내</v>
+        <v>결제 수단 탭(카드·계좌이체·무통장)</v>
       </c>
       <c r="G179" t="str">
-        <v>'계약금 결제' 화면에서 안전거래 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약금 결제'에서 결제 수단 탭(카드·계좌이체·무통장)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H179" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>결제 버튼</v>
+        <v>수단별 입력칸</v>
       </c>
       <c r="G180" t="str">
-        <v>'계약금 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'계약금 결제'의 수단별 입력칸에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H180" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -6578,28 +6578,28 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B181" t="str">
-        <v>계약·결제</v>
+        <v/>
       </c>
       <c r="C181" t="str">
-        <v>결제 완료 - 계약 성사</v>
+        <v/>
       </c>
       <c r="D181" t="str">
-        <v>CT-03</v>
+        <v/>
       </c>
       <c r="E181" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F181" t="str">
-        <v>결제됐다는 체크와 계약 번호</v>
+        <v>할부 개월과 월 납입액 계산</v>
       </c>
       <c r="G181" t="str">
-        <v>'결제 완료 - 계약 성사'에서 결제됐다는 체크와 계약 번호를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'계약금 결제' 화면에서 할부 개월과 월 납입액 계산이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H181" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B182" t="str">
         <v/>
@@ -6625,10 +6625,10 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>계약이 성사됐다는 것과 이제 무엇이 시작되는지</v>
+        <v>현금영수증</v>
       </c>
       <c r="G182" t="str">
-        <v>'결제 완료 - 계약 성사' 화면에서 계약이 성사됐다는 것과 이제 무엇이 시작되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약금 결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H182" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B183" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>착공일 고르기(달력)</v>
+        <v>세금계산서 발급 정보</v>
       </c>
       <c r="G183" t="str">
-        <v>'결제 완료 - 계약 성사' 화면에서 착공일 고르기(달력)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약금 결제'의 세금계산서 발급 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H183" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -6689,13 +6689,13 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>남은 대금 일정 표</v>
+        <v>결제 전 마지막 확인 요약(현장·금액·다음 낼 날)</v>
       </c>
       <c r="G184" t="str">
-        <v>'결제 완료 - 계약 성사'의 남은 대금 일정 표가 실제 데이터와 같은지 대조한다.</v>
+        <v>'계약금 결제'에서 결제 전 마지막 확인 요약(현장·금액·다음 낼 날)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H184" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,10 +6721,10 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>계약서</v>
+        <v>안전거래 안내</v>
       </c>
       <c r="G185" t="str">
-        <v>'결제 완료 - 계약 성사' 화면에서 계약서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약금 결제' 화면에서 안전거래 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H185" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B186" t="str">
         <v/>
@@ -6753,13 +6753,13 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>영수증 내려받기</v>
+        <v>결제 버튼</v>
       </c>
       <c r="G186" t="str">
-        <v>'결제 완료 - 계약 성사' 화면에서 영수증 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'계약금 결제'에서 결제 버튼을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H186" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6773,25 +6773,25 @@
         <v>SCN-019</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>계약·결제</v>
       </c>
       <c r="C187" t="str">
-        <v/>
+        <v>결제 완료 - 계약 성사</v>
       </c>
       <c r="D187" t="str">
-        <v/>
+        <v>CT-03</v>
       </c>
       <c r="E187" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F187" t="str">
-        <v>담당 현장소장 배정 안내와 연락처</v>
+        <v>결제됐다는 체크와 계약 번호</v>
       </c>
       <c r="G187" t="str">
-        <v>'결제 완료 - 계약 성사' 화면에서 담당 현장소장 배정 안내와 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'결제 완료 - 계약 성사'에서 결제됐다는 체크와 계약 번호를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H187" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>착공 전 준비할 것 목록(이사·짐 정리·관리사무소 신고)</v>
+        <v>계약이 성사됐다는 것과 이제 무엇이 시작되는지</v>
       </c>
       <c r="G188" t="str">
-        <v>'결제 완료 - 계약 성사'의 착공 전 준비할 것 목록(이사·짐 정리·관리사무소 신고)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'결제 완료 - 계약 성사' 화면에서 계약이 성사됐다는 것과 이제 무엇이 시작되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H188" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6849,13 +6849,13 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>공사 진행 화면으로 가는 큰 버튼</v>
+        <v>착공일 고르기(달력)</v>
       </c>
       <c r="G189" t="str">
-        <v>'결제 완료 - 계약 성사'에서 공사 진행 화면으로 가는 큰 버튼을 눌러 본다.</v>
+        <v>'결제 완료 - 계약 성사' 화면에서 착공일 고르기(달력)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H189" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -6866,28 +6866,28 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B190" t="str">
-        <v>계약·결제</v>
+        <v/>
       </c>
       <c r="C190" t="str">
-        <v>결제 실패</v>
+        <v/>
       </c>
       <c r="D190" t="str">
-        <v>CT-04</v>
+        <v/>
       </c>
       <c r="E190" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F190" t="str">
-        <v>실패했다는 것과 「돈은 빠져나가지 않았습니다」를 먼저 못 박기</v>
+        <v>남은 대금 일정 표</v>
       </c>
       <c r="G190" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패했다는 것과 「돈은 빠져나가지 않았습니다」를 먼저 못 박기가 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사'의 남은 대금 일정 표가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H190" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B191" t="str">
         <v/>
@@ -6913,13 +6913,13 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>실패 사유와 코드</v>
+        <v>계약서</v>
       </c>
       <c r="G191" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유와 코드가 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사' 화면에서 계약서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H191" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B192" t="str">
         <v/>
@@ -6945,13 +6945,13 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>사유별로 무엇을 하면 되는지 안내</v>
+        <v>영수증 내려받기</v>
       </c>
       <c r="G192" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 사유별로 무엇을 하면 되는지 안내가 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사' 화면에서 영수증 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H192" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -6977,13 +6977,13 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>다시 시도하기와 다른 수단으로 내기 버튼</v>
+        <v>담당 현장소장 배정 안내와 연락처</v>
       </c>
       <c r="G193" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기와 다른 수단으로 내기 버튼이 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사' 화면에서 담당 현장소장 배정 안내와 연락처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H193" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>계약은 아직 살아 있고 며칠까지 결제하면 되는지</v>
+        <v>착공 전 준비할 것 목록(이사·짐 정리·관리사무소 신고)</v>
       </c>
       <c r="G194" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 계약은 아직 살아 있고 며칠까지 결제하면 되는지가 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사'의 착공 전 준비할 것 목록(이사·짐 정리·관리사무소 신고)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H194" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,13 +7041,13 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>무통장으로 돌리기</v>
+        <v>공사 진행 화면으로 가는 큰 버튼</v>
       </c>
       <c r="G195" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 무통장으로 돌리기가 보이는지 확인한다.</v>
+        <v>'결제 완료 - 계약 성사'에서 공사 진행 화면으로 가는 큰 버튼을 눌러 본다.</v>
       </c>
       <c r="H195" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7061,22 +7061,22 @@
         <v>SCN-020</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>계약·결제</v>
       </c>
       <c r="C196" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D196" t="str">
-        <v/>
+        <v>CT-04</v>
       </c>
       <c r="E196" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F196" t="str">
-        <v>전화 상담 연결</v>
+        <v>실패했다는 것과 「돈은 빠져나가지 않았습니다」를 먼저 못 박기</v>
       </c>
       <c r="G196" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 전화 상담 연결이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패했다는 것과 「돈은 빠져나가지 않았습니다」를 먼저 못 박기가 보이는지 확인한다.</v>
       </c>
       <c r="H196" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -7090,28 +7090,28 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B197" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C197" t="str">
-        <v>공정표</v>
+        <v/>
       </c>
       <c r="D197" t="str">
-        <v>PR-01</v>
+        <v/>
       </c>
       <c r="E197" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F197" t="str">
-        <v>전체 진행률과 남은 날수를 맨 위에</v>
+        <v>실패 사유와 코드</v>
       </c>
       <c r="G197" t="str">
-        <v>'공정표'의 전체 진행률과 남은 날수를 맨 위에가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 사유와 코드가 보이는지 확인한다.</v>
       </c>
       <c r="H197" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I197" t="str">
         <v/>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B198" t="str">
         <v/>
@@ -7137,13 +7137,13 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>공정별 가로 막대 일정표(철거·설비·전기·목공·타일·도배·마루·조명·청소)와 오늘 선</v>
+        <v>사유별로 무엇을 하면 되는지 안내</v>
       </c>
       <c r="G198" t="str">
-        <v>'공정표' 화면에서 공정별 가로 막대 일정표(철거·설비·전기·목공·타일·도배·마루·조명·청소)와 오늘 선이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 사유별로 무엇을 하면 되는지 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H198" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -7169,13 +7169,13 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>공정 상태 배지(끝남·하는 중·기다림·밀림)</v>
+        <v>다시 시도하기와 다른 수단으로 내기 버튼</v>
       </c>
       <c r="G199" t="str">
-        <v>'공정표'의 공정 상태 배지(끝남·하는 중·기다림·밀림)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기와 다른 수단으로 내기 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H199" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B200" t="str">
         <v/>
@@ -7201,13 +7201,13 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>막대를 누르면 펼쳐지는 세부 일정과 담당 팀</v>
+        <v>계약은 아직 살아 있고 며칠까지 결제하면 되는지</v>
       </c>
       <c r="G200" t="str">
-        <v>'공정표' 화면에서 막대를 누르면 펼쳐지는 세부 일정과 담당 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 계약은 아직 살아 있고 며칠까지 결제하면 되는지가 보이는지 확인한다.</v>
       </c>
       <c r="H200" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -7218,7 +7218,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B201" t="str">
         <v/>
@@ -7233,13 +7233,13 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>앞 공정이 밀리면 뒤가 어떻게 밀리는지 표시</v>
+        <v>무통장으로 돌리기</v>
       </c>
       <c r="G201" t="str">
-        <v>'공정표'의 앞 공정이 밀리면 뒤가 어떻게 밀리는지 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 무통장으로 돌리기가 보이는지 확인한다.</v>
       </c>
       <c r="H201" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B202" t="str">
         <v/>
@@ -7265,13 +7265,13 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>주 보기와 월 보기 전환</v>
+        <v>전화 상담 연결</v>
       </c>
       <c r="G202" t="str">
-        <v>'공정표' 화면에서 주 보기와 월 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 전화 상담 연결이 보이는지 확인한다.</v>
       </c>
       <c r="H202" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7285,25 +7285,25 @@
         <v>SCN-021</v>
       </c>
       <c r="B203" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C203" t="str">
-        <v/>
+        <v>공정표</v>
       </c>
       <c r="D203" t="str">
-        <v/>
+        <v>PR-01</v>
       </c>
       <c r="E203" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F203" t="str">
-        <v>이번 주에 있을 일 목록</v>
+        <v>전체 진행률과 남은 날수를 맨 위에</v>
       </c>
       <c r="G203" t="str">
-        <v>'공정표'의 이번 주에 있을 일 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'공정표'의 전체 진행률과 남은 날수를 맨 위에가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H203" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I203" t="str">
         <v/>
@@ -7329,10 +7329,10 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>공정별 진행 사진으로 가는 길</v>
+        <v>공정별 가로 막대 일정표(철거·설비·전기·목공·타일·도배·마루·조명·청소)와 오늘 선</v>
       </c>
       <c r="G204" t="str">
-        <v>'공정표' 화면에서 공정별 진행 사진으로 가는 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표' 화면에서 공정별 가로 막대 일정표(철거·설비·전기·목공·타일·도배·마루·조명·청소)와 오늘 선이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7346,28 +7346,28 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B205" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C205" t="str">
-        <v>오늘 현장</v>
+        <v/>
       </c>
       <c r="D205" t="str">
-        <v>PR-02</v>
+        <v/>
       </c>
       <c r="E205" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F205" t="str">
-        <v>오늘 날짜와 며칠째인지</v>
+        <v>공정 상태 배지(끝남·하는 중·기다림·밀림)</v>
       </c>
       <c r="G205" t="str">
-        <v>'오늘 현장' 화면에서 오늘 날짜와 며칠째인지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표'의 공정 상태 배지(끝남·하는 중·기다림·밀림)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H205" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I205" t="str">
         <v/>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,10 +7393,10 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>오늘 진행 중인 공정과 현장에 온 팀</v>
+        <v>막대를 누르면 펼쳐지는 세부 일정과 담당 팀</v>
       </c>
       <c r="G206" t="str">
-        <v>'오늘 현장' 화면에서 오늘 진행 중인 공정과 현장에 온 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표' 화면에서 막대를 누르면 펼쳐지는 세부 일정과 담당 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,13 +7425,13 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>오늘 찍은 사진 줄</v>
+        <v>앞 공정이 밀리면 뒤가 어떻게 밀리는지 표시</v>
       </c>
       <c r="G207" t="str">
-        <v>'오늘 현장' 화면에서 오늘 찍은 사진 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표'의 앞 공정이 밀리면 뒤가 어떻게 밀리는지 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H207" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B208" t="str">
         <v/>
@@ -7457,10 +7457,10 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>현장소장이 남긴 오늘의 한마디</v>
+        <v>주 보기와 월 보기 전환</v>
       </c>
       <c r="G208" t="str">
-        <v>'오늘 현장' 화면에서 현장소장이 남긴 오늘의 한마디가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표' 화면에서 주 보기와 월 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B209" t="str">
         <v/>
@@ -7489,10 +7489,10 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>오늘 끝난 일과 내일 할 일 목록</v>
+        <v>이번 주에 있을 일 목록</v>
       </c>
       <c r="G209" t="str">
-        <v>'오늘 현장'의 오늘 끝난 일과 내일 할 일 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'공정표'의 이번 주에 있을 일 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
         <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B210" t="str">
         <v/>
@@ -7521,10 +7521,10 @@
         <v/>
       </c>
       <c r="F210" t="str">
-        <v>집주인이 오늘 정해 줘야 할 것(있으면 위로 올라온다)</v>
+        <v>공정별 진행 사진으로 가는 길</v>
       </c>
       <c r="G210" t="str">
-        <v>'오늘 현장' 화면에서 집주인이 오늘 정해 줘야 할 것(있으면 위로 올라온다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'공정표' 화면에서 공정별 진행 사진으로 가는 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H210" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7541,22 +7541,22 @@
         <v>SCN-022</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C211" t="str">
-        <v/>
+        <v>오늘 현장</v>
       </c>
       <c r="D211" t="str">
-        <v/>
+        <v>PR-02</v>
       </c>
       <c r="E211" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F211" t="str">
-        <v>소장에게 바로 묻는 말풍선</v>
+        <v>오늘 날짜와 며칠째인지</v>
       </c>
       <c r="G211" t="str">
-        <v>'오늘 현장' 화면에서 소장에게 바로 묻는 말풍선이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 오늘 날짜와 며칠째인지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H211" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7585,10 +7585,10 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>날씨와 그 때문에 밀릴 수 있는 공정 안내</v>
+        <v>오늘 진행 중인 공정과 현장에 온 팀</v>
       </c>
       <c r="G212" t="str">
-        <v>'오늘 현장' 화면에서 날씨와 그 때문에 밀릴 수 있는 공정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 오늘 진행 중인 공정과 현장에 온 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7617,10 +7617,10 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>어제</v>
+        <v>오늘 찍은 사진 줄</v>
       </c>
       <c r="G213" t="str">
-        <v>'오늘 현장' 화면에서 어제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 오늘 찍은 사진 줄이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H213" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7649,10 +7649,10 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>내일로 넘기는 화살표</v>
+        <v>현장소장이 남긴 오늘의 한마디</v>
       </c>
       <c r="G214" t="str">
-        <v>'오늘 현장' 화면에서 내일로 넘기는 화살표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 현장소장이 남긴 오늘의 한마디가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H214" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7666,28 +7666,28 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B215" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C215" t="str">
-        <v>현장 사진 일지</v>
+        <v/>
       </c>
       <c r="D215" t="str">
-        <v>PR-03</v>
+        <v/>
       </c>
       <c r="E215" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F215" t="str">
-        <v>날짜별로 묶인 사진 일지(최신이 위)</v>
+        <v>오늘 끝난 일과 내일 할 일 목록</v>
       </c>
       <c r="G215" t="str">
-        <v>'현장 사진 일지' 화면에서 날짜별로 묶인 사진 일지(최신이 위)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장'의 오늘 끝난 일과 내일 할 일 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B216" t="str">
         <v/>
@@ -7713,13 +7713,13 @@
         <v/>
       </c>
       <c r="F216" t="str">
-        <v>공정 필터 칩과 공간 필터 칩</v>
+        <v>집주인이 오늘 정해 줘야 할 것(있으면 위로 올라온다)</v>
       </c>
       <c r="G216" t="str">
-        <v>'현장 사진 일지'에서 공정 필터 칩과 공간 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'오늘 현장' 화면에서 집주인이 오늘 정해 줘야 할 것(있으면 위로 올라온다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H216" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B217" t="str">
         <v/>
@@ -7745,10 +7745,10 @@
         <v/>
       </c>
       <c r="F217" t="str">
-        <v>날짜 묶음마다 그날 공정</v>
+        <v>소장에게 바로 묻는 말풍선</v>
       </c>
       <c r="G217" t="str">
-        <v>'현장 사진 일지' 화면에서 날짜 묶음마다 그날 공정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 소장에게 바로 묻는 말풍선이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H217" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B218" t="str">
         <v/>
@@ -7777,10 +7777,10 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>팀</v>
+        <v>날씨와 그 때문에 밀릴 수 있는 공정 안내</v>
       </c>
       <c r="G218" t="str">
-        <v>'현장 사진 일지' 화면에서 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 날씨와 그 때문에 밀릴 수 있는 공정 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B219" t="str">
         <v/>
@@ -7809,10 +7809,10 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>사진 장수</v>
+        <v>어제</v>
       </c>
       <c r="G219" t="str">
-        <v>'현장 사진 일지' 화면에서 사진 장수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 어제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H219" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B220" t="str">
         <v/>
@@ -7841,10 +7841,10 @@
         <v/>
       </c>
       <c r="F220" t="str">
-        <v>사진 격자와 찍은 시각</v>
+        <v>내일로 넘기는 화살표</v>
       </c>
       <c r="G220" t="str">
-        <v>'현장 사진 일지' 화면에서 사진 격자와 찍은 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'오늘 현장' 화면에서 내일로 넘기는 화살표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H220" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7861,22 +7861,22 @@
         <v>SCN-023</v>
       </c>
       <c r="B221" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C221" t="str">
-        <v/>
+        <v>현장 사진 일지</v>
       </c>
       <c r="D221" t="str">
-        <v/>
+        <v>PR-03</v>
       </c>
       <c r="E221" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F221" t="str">
-        <v>공간 꼬리표</v>
+        <v>날짜별로 묶인 사진 일지(최신이 위)</v>
       </c>
       <c r="G221" t="str">
-        <v>'현장 사진 일지' 화면에서 공간 꼬리표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 날짜별로 묶인 사진 일지(최신이 위)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H221" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7905,13 +7905,13 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v>사진에 달린 소장 설명</v>
+        <v>공정 필터 칩과 공간 필터 칩</v>
       </c>
       <c r="G222" t="str">
-        <v>'현장 사진 일지' 화면에서 사진에 달린 소장 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지'에서 공정 필터 칩과 공간 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H222" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -7937,10 +7937,10 @@
         <v/>
       </c>
       <c r="F223" t="str">
-        <v>같은 자리를 날짜별로 견주어 보는 「이 자리 변해 온 것」</v>
+        <v>날짜 묶음마다 그날 공정</v>
       </c>
       <c r="G223" t="str">
-        <v>'현장 사진 일지' 화면에서 같은 자리를 날짜별로 견주어 보는 「이 자리 변해 온 것」이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 날짜 묶음마다 그날 공정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H223" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7969,10 +7969,10 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>전체 사진 내려받기</v>
+        <v>팀</v>
       </c>
       <c r="G224" t="str">
-        <v>'현장 사진 일지' 화면에서 전체 사진 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 팀이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H224" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8001,10 +8001,10 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>준공 앨범으로 묶기</v>
+        <v>사진 장수</v>
       </c>
       <c r="G225" t="str">
-        <v>'현장 사진 일지' 화면에서 준공 앨범으로 묶기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 사진 장수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H225" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8018,25 +8018,25 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B226" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C226" t="str">
-        <v>추가공사 변경 견적 승인</v>
+        <v/>
       </c>
       <c r="D226" t="str">
-        <v>PR-04</v>
+        <v/>
       </c>
       <c r="E226" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F226" t="str">
-        <v>왜 추가공사가 생겼는지 먼저 설명(현장 사진과 함께)</v>
+        <v>사진 격자와 찍은 시각</v>
       </c>
       <c r="G226" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 왜 추가공사가 생겼는지 먼저 설명(현장 사진과 함께)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 사진 격자와 찍은 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H226" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B227" t="str">
         <v/>
@@ -8065,10 +8065,10 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>추가 항목 표(내용·수량·단가·금액·왜 필요한지)</v>
+        <v>공간 꼬리표</v>
       </c>
       <c r="G227" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 추가 항목 표(내용·수량·단가·금액·왜 필요한지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 공간 꼬리표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H227" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B228" t="str">
         <v/>
@@ -8097,10 +8097,10 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>항목마다 승인</v>
+        <v>사진에 달린 소장 설명</v>
       </c>
       <c r="G228" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 항목마다 승인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 사진에 달린 소장 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H228" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B229" t="str">
         <v/>
@@ -8129,10 +8129,10 @@
         <v/>
       </c>
       <c r="F229" t="str">
-        <v>거절을 따로 고르는 것</v>
+        <v>같은 자리를 날짜별로 견주어 보는 「이 자리 변해 온 것」</v>
       </c>
       <c r="G229" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 거절을 따로 고르는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 같은 자리를 날짜별로 견주어 보는 「이 자리 변해 온 것」이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H229" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B230" t="str">
         <v/>
@@ -8161,10 +8161,10 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>거절하면 어떻게 되는지 경고</v>
+        <v>전체 사진 내려받기</v>
       </c>
       <c r="G230" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 거절하면 어떻게 되는지 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 전체 사진 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H230" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B231" t="str">
         <v/>
@@ -8193,10 +8193,10 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>승인하면 공사 기간이 며칠 늘어나는지</v>
+        <v>준공 앨범으로 묶기</v>
       </c>
       <c r="G231" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 승인하면 공사 기간이 며칠 늘어나는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 사진 일지' 화면에서 준공 앨범으로 묶기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H231" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8213,25 +8213,25 @@
         <v>SCN-024</v>
       </c>
       <c r="B232" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C232" t="str">
-        <v/>
+        <v>추가공사 변경 견적 승인</v>
       </c>
       <c r="D232" t="str">
-        <v/>
+        <v>PR-04</v>
       </c>
       <c r="E232" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F232" t="str">
-        <v>바뀐 총액과 남은 대금 일정 재계산</v>
+        <v>왜 추가공사가 생겼는지 먼저 설명(현장 사진과 함께)</v>
       </c>
       <c r="G232" t="str">
-        <v>'추가공사 변경 견적 승인'의 바뀐 총액과 남은 대금 일정 재계산이 실제 데이터와 같은지 대조한다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 왜 추가공사가 생겼는지 먼저 설명(현장 사진과 함께)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H232" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8257,10 +8257,10 @@
         <v/>
       </c>
       <c r="F233" t="str">
-        <v>승인 체크와 서명</v>
+        <v>추가 항목 표(내용·수량·단가·금액·왜 필요한지)</v>
       </c>
       <c r="G233" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 승인 체크와 서명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 추가 항목 표(내용·수량·단가·금액·왜 필요한지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8289,10 +8289,10 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>「나중에 정하기」와 그 경우 공사가 멈추는 자리 안내</v>
+        <v>항목마다 승인</v>
       </c>
       <c r="G234" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 「나중에 정하기」와 그 경우 공사가 멈추는 자리 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 항목마다 승인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H234" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8321,10 +8321,10 @@
         <v/>
       </c>
       <c r="F235" t="str">
-        <v>소장에게 묻기</v>
+        <v>거절을 따로 고르는 것</v>
       </c>
       <c r="G235" t="str">
-        <v>'추가공사 변경 견적 승인' 화면에서 소장에게 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 거절을 따로 고르는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H235" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8338,28 +8338,28 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B236" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C236" t="str">
-        <v>준공 검수 체크리스트</v>
+        <v/>
       </c>
       <c r="D236" t="str">
-        <v>PR-05</v>
+        <v/>
       </c>
       <c r="E236" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F236" t="str">
-        <v>공간 탭(거실·주방·욕실·침실·베란다·공용)</v>
+        <v>거절하면 어떻게 되는지 경고</v>
       </c>
       <c r="G236" t="str">
-        <v>'준공 검수 체크리스트'에서 공간 탭(거실·주방·욕실·침실·베란다·공용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 거절하면 어떻게 되는지 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H236" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B237" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>공간별 검수 항목 체크 목록(마감·수평·문 여닫힘·수전 누수·콘센트·조명)</v>
+        <v>승인하면 공사 기간이 며칠 늘어나는지</v>
       </c>
       <c r="G237" t="str">
-        <v>'준공 검수 체크리스트'의 공간별 검수 항목 체크 목록(마감·수평·문 여닫힘·수전 누수·콘센트·조명)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 승인하면 공사 기간이 며칠 늘어나는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H237" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B238" t="str">
         <v/>
@@ -8417,13 +8417,13 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>항목마다 「괜찮음</v>
+        <v>바뀐 총액과 남은 대금 일정 재계산</v>
       </c>
       <c r="G238" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 항목마다 「괜찮음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인'의 바뀐 총액과 남은 대금 일정 재계산이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H238" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I238" t="str">
         <v/>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B239" t="str">
         <v/>
@@ -8449,10 +8449,10 @@
         <v/>
       </c>
       <c r="F239" t="str">
-        <v>문제 있음」 두 갈래</v>
+        <v>승인 체크와 서명</v>
       </c>
       <c r="G239" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 문제 있음」 두 갈래가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 승인 체크와 서명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,10 +8481,10 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>문제 있음을 고르면 열리는 사진 올리기와 메모</v>
+        <v>「나중에 정하기」와 그 경우 공사가 멈추는 자리 안내</v>
       </c>
       <c r="G240" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 문제 있음을 고르면 열리는 사진 올리기와 메모가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 「나중에 정하기」와 그 경우 공사가 멈추는 자리 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B241" t="str">
         <v/>
@@ -8513,10 +8513,10 @@
         <v/>
       </c>
       <c r="F241" t="str">
-        <v>검수 진행 숫자(48개 중 41개 확인)</v>
+        <v>소장에게 묻기</v>
       </c>
       <c r="G241" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 검수 진행 숫자(48개 중 41개 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'추가공사 변경 견적 승인' 화면에서 소장에게 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H241" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8533,25 +8533,25 @@
         <v>SCN-025</v>
       </c>
       <c r="B242" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C242" t="str">
-        <v/>
+        <v>준공 검수 체크리스트</v>
       </c>
       <c r="D242" t="str">
-        <v/>
+        <v>PR-05</v>
       </c>
       <c r="E242" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F242" t="str">
-        <v>문제로 잡힌 것 모아 보기</v>
+        <v>공간 탭(거실·주방·욕실·침실·베란다·공용)</v>
       </c>
       <c r="G242" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 문제로 잡힌 것 모아 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'준공 검수 체크리스트'에서 공간 탭(거실·주방·욕실·침실·베란다·공용)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H242" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8577,13 +8577,13 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>재시공 요청과 처리 기한 안내</v>
+        <v>공간별 검수 항목 체크 목록(마감·수평·문 여닫힘·수전 누수·콘센트·조명)</v>
       </c>
       <c r="G243" t="str">
-        <v>'준공 검수 체크리스트' 화면에서 재시공 요청과 처리 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'준공 검수 체크리스트'의 공간별 검수 항목 체크 목록(마감·수평·문 여닫힘·수전 누수·콘센트·조명)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H243" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I243" t="str">
         <v/>
@@ -8609,13 +8609,13 @@
         <v/>
       </c>
       <c r="F244" t="str">
-        <v>다 끝나면 열리는 준공 승인 버튼</v>
+        <v>항목마다 「괜찮음</v>
       </c>
       <c r="G244" t="str">
-        <v>'준공 검수 체크리스트'에서 다 끝나면 열리는 준공 승인 버튼을 눌러 본다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 항목마다 「괜찮음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H244" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I244" t="str">
         <v/>
@@ -8641,13 +8641,13 @@
         <v/>
       </c>
       <c r="F245" t="str">
-        <v>잔금 결제로 이어지는 길</v>
+        <v>문제 있음」 두 갈래</v>
       </c>
       <c r="G245" t="str">
-        <v>'준공 검수 체크리스트'에서 잔금 결제로 이어지는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 문제 있음」 두 갈래가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I245" t="str">
         <v/>
@@ -8658,28 +8658,28 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B246" t="str">
-        <v>공사 진행</v>
+        <v/>
       </c>
       <c r="C246" t="str">
-        <v>공사 진행 - 진행 중 없음</v>
+        <v/>
       </c>
       <c r="D246" t="str">
-        <v>PR-06</v>
+        <v/>
       </c>
       <c r="E246" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F246" t="str">
-        <v>지금 진행 중인 공사가 없다는 안내</v>
+        <v>문제 있음을 고르면 열리는 사진 올리기와 메모</v>
       </c>
       <c r="G246" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 지금 진행 중인 공사가 없다는 안내가 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 문제 있음을 고르면 열리는 사진 올리기와 메모가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I246" t="str">
         <v/>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B247" t="str">
         <v/>
@@ -8705,13 +8705,13 @@
         <v/>
       </c>
       <c r="F247" t="str">
-        <v>왜 비어 있는지(아직 계약 전이거나 다 끝났거나)에 따라 다른 문구</v>
+        <v>검수 진행 숫자(48개 중 41개 확인)</v>
       </c>
       <c r="G247" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 왜 비어 있는지(아직 계약 전이거나 다 끝났거나)에 따라 다른 문구가 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 검수 진행 숫자(48개 중 41개 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H247" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>계약 전이라면 견적</v>
+        <v>문제로 잡힌 것 모아 보기</v>
       </c>
       <c r="G248" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 계약 전이라면 견적이 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 문제로 잡힌 것 모아 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>실측으로 가는 길</v>
+        <v>재시공 요청과 처리 기한 안내</v>
       </c>
       <c r="G249" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 실측으로 가는 길이 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트' 화면에서 재시공 요청과 처리 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H249" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B250" t="str">
         <v/>
@@ -8801,13 +8801,13 @@
         <v/>
       </c>
       <c r="F250" t="str">
-        <v>끝난 공사가 있으면 준공 앨범과 하자보수로 가는 길</v>
+        <v>다 끝나면 열리는 준공 승인 버튼</v>
       </c>
       <c r="G250" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 끝난 공사가 있으면 준공 앨범과 하자보수로 가는 길이 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트'에서 다 끝나면 열리는 준공 승인 버튼을 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -8818,7 +8818,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B251" t="str">
         <v/>
@@ -8833,13 +8833,13 @@
         <v/>
       </c>
       <c r="F251" t="str">
-        <v>지난 공사 목록 접어 두기</v>
+        <v>잔금 결제로 이어지는 길</v>
       </c>
       <c r="G251" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 지난 공사 목록 접어 두기가 보이는지 확인한다.</v>
+        <v>'준공 검수 체크리스트'에서 잔금 결제로 이어지는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8853,22 +8853,22 @@
         <v>SCN-026</v>
       </c>
       <c r="B252" t="str">
-        <v/>
+        <v>공사 진행</v>
       </c>
       <c r="C252" t="str">
-        <v/>
+        <v>공사 진행 - 진행 중 없음</v>
       </c>
       <c r="D252" t="str">
-        <v/>
+        <v>PR-06</v>
       </c>
       <c r="E252" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F252" t="str">
-        <v>하자보수 보증 기간이 얼마나 남았는지</v>
+        <v>지금 진행 중인 공사가 없다는 안내</v>
       </c>
       <c r="G252" t="str">
-        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 하자보수 보증 기간이 얼마나 남았는지가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 지금 진행 중인 공사가 없다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H252" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8882,28 +8882,28 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B253" t="str">
-        <v>하자보수</v>
+        <v/>
       </c>
       <c r="C253" t="str">
-        <v>하자보수 접수</v>
+        <v/>
       </c>
       <c r="D253" t="str">
-        <v>AS-01</v>
+        <v/>
       </c>
       <c r="E253" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F253" t="str">
-        <v>보증 기간이 얼마나 남았는지 맨 위에</v>
+        <v>왜 비어 있는지(아직 계약 전이거나 다 끝났거나)에 따라 다른 문구</v>
       </c>
       <c r="G253" t="str">
-        <v>'하자보수 접수' 화면에서 보증 기간이 얼마나 남았는지 맨 위에가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 왜 비어 있는지(아직 계약 전이거나 다 끝났거나)에 따라 다른 문구가 보이는지 확인한다.</v>
       </c>
       <c r="H253" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B254" t="str">
         <v/>
@@ -8929,13 +8929,13 @@
         <v/>
       </c>
       <c r="F254" t="str">
-        <v>어느 현장인지 고르기(여러 곳이면)</v>
+        <v>계약 전이라면 견적</v>
       </c>
       <c r="G254" t="str">
-        <v>'하자보수 접수' 화면에서 어느 현장인지 고르기(여러 곳이면)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 계약 전이라면 견적이 보이는지 확인한다.</v>
       </c>
       <c r="H254" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B255" t="str">
         <v/>
@@ -8961,13 +8961,13 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>부위 고르기(도배·바닥·타일·설비·전기·창호·목공)와 부위에 맞게 바뀌는 증상 목록</v>
+        <v>실측으로 가는 길</v>
       </c>
       <c r="G255" t="str">
-        <v>'하자보수 접수' 화면에서 부위 고르기(도배·바닥·타일·설비·전기·창호·목공)와 부위에 맞게 바뀌는 증상 목록이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 실측으로 가는 길이 보이는지 확인한다.</v>
       </c>
       <c r="H255" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B256" t="str">
         <v/>
@@ -8993,13 +8993,13 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>사진</v>
+        <v>끝난 공사가 있으면 준공 앨범과 하자보수로 가는 길</v>
       </c>
       <c r="G256" t="str">
-        <v>'하자보수 접수' 화면에서 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 끝난 공사가 있으면 준공 앨범과 하자보수로 가는 길이 보이는지 확인한다.</v>
       </c>
       <c r="H256" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B257" t="str">
         <v/>
@@ -9025,13 +9025,13 @@
         <v/>
       </c>
       <c r="F257" t="str">
-        <v>영상 올리기</v>
+        <v>지난 공사 목록 접어 두기</v>
       </c>
       <c r="G257" t="str">
-        <v>'하자보수 접수' 화면에서 영상 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 지난 공사 목록 접어 두기가 보이는지 확인한다.</v>
       </c>
       <c r="H257" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B258" t="str">
         <v/>
@@ -9057,13 +9057,13 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>자세한 상황 적는 칸</v>
+        <v>하자보수 보증 기간이 얼마나 남았는지</v>
       </c>
       <c r="G258" t="str">
-        <v>'하자보수 접수' 화면에서 자세한 상황 적는 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '공사 진행 - 진행 중 없음' 화면이 나오게 한 뒤, 하자보수 보증 기간이 얼마나 남았는지가 보이는지 확인한다.</v>
       </c>
       <c r="H258" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9077,25 +9077,25 @@
         <v>SCN-027</v>
       </c>
       <c r="B259" t="str">
-        <v/>
+        <v>하자보수</v>
       </c>
       <c r="C259" t="str">
-        <v/>
+        <v>하자보수 접수</v>
       </c>
       <c r="D259" t="str">
-        <v/>
+        <v>AS-01</v>
       </c>
       <c r="E259" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F259" t="str">
-        <v>급한 정도 3단(급함·보통·천천히)과 그에 따른 예상 방문일</v>
+        <v>보증 기간이 얼마나 남았는지 맨 위에</v>
       </c>
       <c r="G259" t="str">
-        <v>'하자보수 접수' 화면을 열고 급한 정도 3단(급함·보통·천천히)과 그에 따른 예상 방문일이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'하자보수 접수' 화면에서 보증 기간이 얼마나 남았는지 맨 위에가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9121,10 +9121,10 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>방문 가능한 요일</v>
+        <v>어느 현장인지 고르기(여러 곳이면)</v>
       </c>
       <c r="G260" t="str">
-        <v>'하자보수 접수' 화면에서 방문 가능한 요일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 어느 현장인지 고르기(여러 곳이면)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H260" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9153,10 +9153,10 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>시간대 고르기</v>
+        <v>부위 고르기(도배·바닥·타일·설비·전기·창호·목공)와 부위에 맞게 바뀌는 증상 목록</v>
       </c>
       <c r="G261" t="str">
-        <v>'하자보수 접수' 화면에서 시간대 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 부위 고르기(도배·바닥·타일·설비·전기·창호·목공)와 부위에 맞게 바뀌는 증상 목록이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H261" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9185,10 +9185,10 @@
         <v/>
       </c>
       <c r="F262" t="str">
-        <v>보증에 들어가는 것과 안 들어가는 것 안내</v>
+        <v>사진</v>
       </c>
       <c r="G262" t="str">
-        <v>'하자보수 접수' 화면에서 보증에 들어가는 것과 안 들어가는 것 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H262" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9217,13 +9217,13 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>접수 버튼</v>
+        <v>영상 올리기</v>
       </c>
       <c r="G263" t="str">
-        <v>'하자보수 접수'에서 접수 버튼을 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 영상 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H263" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9234,28 +9234,28 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B264" t="str">
-        <v>하자보수</v>
+        <v/>
       </c>
       <c r="C264" t="str">
-        <v>하자보수 접수 내역</v>
+        <v/>
       </c>
       <c r="D264" t="str">
-        <v>AS-02</v>
+        <v/>
       </c>
       <c r="E264" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F264" t="str">
-        <v>상태 탭(전체·접수됨·방문 예정·처리 중·완료)</v>
+        <v>자세한 상황 적는 칸</v>
       </c>
       <c r="G264" t="str">
-        <v>'하자보수 접수 내역'에서 상태 탭(전체·접수됨·방문 예정·처리 중·완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'하자보수 접수' 화면에서 자세한 상황 적는 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H264" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B265" t="str">
         <v/>
@@ -9281,13 +9281,13 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>접수 건 목록(접수일·부위·증상·상태 배지·예상 방문일)</v>
+        <v>급한 정도 3단(급함·보통·천천히)과 그에 따른 예상 방문일</v>
       </c>
       <c r="G265" t="str">
-        <v>'하자보수 접수 내역'의 접수 건 목록(접수일·부위·증상·상태 배지·예상 방문일)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'하자보수 접수' 화면을 열고 급한 정도 3단(급함·보통·천천히)과 그에 따른 예상 방문일이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H265" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B266" t="str">
         <v/>
@@ -9313,10 +9313,10 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>줄을 펼치면 나오는 진행 단계 막대와 사진</v>
+        <v>방문 가능한 요일</v>
       </c>
       <c r="G266" t="str">
-        <v>'하자보수 접수 내역' 화면에서 줄을 펼치면 나오는 진행 단계 막대와 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 방문 가능한 요일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H266" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -9345,10 +9345,10 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>급한 건은 위로</v>
+        <v>시간대 고르기</v>
       </c>
       <c r="G267" t="str">
-        <v>'하자보수 접수 내역' 화면에서 급한 건은 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수' 화면에서 시간대 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B268" t="str">
         <v/>
@@ -9377,13 +9377,13 @@
         <v/>
       </c>
       <c r="F268" t="str">
-        <v>처리가 늦어지는 건에 붙는 표시</v>
+        <v>보증에 들어가는 것과 안 들어가는 것 안내</v>
       </c>
       <c r="G268" t="str">
-        <v>'하자보수 접수 내역'의 처리가 늦어지는 건에 붙는 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'하자보수 접수' 화면에서 보증에 들어가는 것과 안 들어가는 것 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H268" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B269" t="str">
         <v/>
@@ -9409,13 +9409,13 @@
         <v/>
       </c>
       <c r="F269" t="str">
-        <v>접수 건이 없을 때 안내</v>
+        <v>접수 버튼</v>
       </c>
       <c r="G269" t="str">
-        <v>'하자보수 접수 내역' 화면에서 접수 건이 없을 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수'에서 접수 버튼을 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I269" t="str">
         <v/>
@@ -9429,25 +9429,25 @@
         <v>SCN-028</v>
       </c>
       <c r="B270" t="str">
-        <v/>
+        <v>하자보수</v>
       </c>
       <c r="C270" t="str">
-        <v/>
+        <v>하자보수 접수 내역</v>
       </c>
       <c r="D270" t="str">
-        <v/>
+        <v>AS-02</v>
       </c>
       <c r="E270" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F270" t="str">
-        <v>새로 접수하기 버튼</v>
+        <v>상태 탭(전체·접수됨·방문 예정·처리 중·완료)</v>
       </c>
       <c r="G270" t="str">
-        <v>'하자보수 접수 내역'에서 새로 접수하기 버튼을 눌러 본다.</v>
+        <v>'하자보수 접수 내역'에서 상태 탭(전체·접수됨·방문 예정·처리 중·완료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H270" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I270" t="str">
         <v/>
@@ -9473,13 +9473,13 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>보증 기간 남은 날</v>
+        <v>접수 건 목록(접수일·부위·증상·상태 배지·예상 방문일)</v>
       </c>
       <c r="G271" t="str">
-        <v>'하자보수 접수 내역'의 보증 기간 남은 날이 실제 데이터와 같은지 대조한다.</v>
+        <v>'하자보수 접수 내역'의 접수 건 목록(접수일·부위·증상·상태 배지·예상 방문일)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H271" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9490,25 +9490,25 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B272" t="str">
-        <v>하자보수</v>
+        <v/>
       </c>
       <c r="C272" t="str">
-        <v>하자보수 처리 현황</v>
+        <v/>
       </c>
       <c r="D272" t="str">
-        <v>AS-03</v>
+        <v/>
       </c>
       <c r="E272" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F272" t="str">
-        <v>접수 번호와 지금 어느 단계인지 큰 막대</v>
+        <v>줄을 펼치면 나오는 진행 단계 막대와 사진</v>
       </c>
       <c r="G272" t="str">
-        <v>'하자보수 처리 현황' 화면에서 접수 번호와 지금 어느 단계인지 큰 막대가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수 내역' 화면에서 줄을 펼치면 나오는 진행 단계 막대와 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -9537,10 +9537,10 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>접수 내용 요약(부위·증상·올린 사진)</v>
+        <v>급한 건은 위로</v>
       </c>
       <c r="G273" t="str">
-        <v>'하자보수 처리 현황' 화면에서 접수 내용 요약(부위·증상·올린 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수 내역' 화면에서 급한 건은 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H273" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -9569,13 +9569,13 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>담당 기사 카드와 방문 예정 일시</v>
+        <v>처리가 늦어지는 건에 붙는 표시</v>
       </c>
       <c r="G274" t="str">
-        <v>'하자보수 처리 현황'의 담당 기사 카드와 방문 예정 일시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'하자보수 접수 내역'의 처리가 늦어지는 건에 붙는 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H274" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B275" t="str">
         <v/>
@@ -9601,10 +9601,10 @@
         <v/>
       </c>
       <c r="F275" t="str">
-        <v>처리 기록 시간순(접수·확인·방문·처리·완료)</v>
+        <v>접수 건이 없을 때 안내</v>
       </c>
       <c r="G275" t="str">
-        <v>'하자보수 처리 현황' 화면에서 처리 기록 시간순(접수·확인·방문·처리·완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수 내역' 화면에서 접수 건이 없을 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B276" t="str">
         <v/>
@@ -9633,13 +9633,13 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>처리 전</v>
+        <v>새로 접수하기 버튼</v>
       </c>
       <c r="G276" t="str">
-        <v>'하자보수 처리 현황' 화면에서 처리 전이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수 내역'에서 새로 접수하기 버튼을 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I276" t="str">
         <v/>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B277" t="str">
         <v/>
@@ -9665,13 +9665,13 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>후 사진 견주기</v>
+        <v>보증 기간 남은 날</v>
       </c>
       <c r="G277" t="str">
-        <v>'하자보수 처리 현황' 화면에서 후 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 접수 내역'의 보증 기간 남은 날이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H277" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -9685,22 +9685,22 @@
         <v>SCN-029</v>
       </c>
       <c r="B278" t="str">
-        <v/>
+        <v>하자보수</v>
       </c>
       <c r="C278" t="str">
-        <v/>
+        <v>하자보수 처리 현황</v>
       </c>
       <c r="D278" t="str">
-        <v/>
+        <v>AS-03</v>
       </c>
       <c r="E278" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F278" t="str">
-        <v>원인과 무엇을 했는지 설명</v>
+        <v>접수 번호와 지금 어느 단계인지 큰 막대</v>
       </c>
       <c r="G278" t="str">
-        <v>'하자보수 처리 현황' 화면에서 원인과 무엇을 했는지 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 접수 번호와 지금 어느 단계인지 큰 막대가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9729,10 +9729,10 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>이번 처리가 보증에 들어갔는지 비용이 붙었는지</v>
+        <v>접수 내용 요약(부위·증상·올린 사진)</v>
       </c>
       <c r="G279" t="str">
-        <v>'하자보수 처리 현황' 화면에서 이번 처리가 보증에 들어갔는지 비용이 붙었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 접수 내용 요약(부위·증상·올린 사진)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H279" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9761,13 +9761,13 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v>처리 확인 체크와 완료 버튼</v>
+        <v>담당 기사 카드와 방문 예정 일시</v>
       </c>
       <c r="G280" t="str">
-        <v>'하자보수 처리 현황'에서 처리 확인 체크와 완료 버튼을 눌러 본다.</v>
+        <v>'하자보수 처리 현황'의 담당 기사 카드와 방문 예정 일시를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H280" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -9793,10 +9793,10 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>「다시 봐 주세요」 재접수</v>
+        <v>처리 기록 시간순(접수·확인·방문·처리·완료)</v>
       </c>
       <c r="G281" t="str">
-        <v>'하자보수 처리 현황' 화면에서 「다시 봐 주세요」 재접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 처리 기록 시간순(접수·확인·방문·처리·완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H281" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9825,10 +9825,10 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v>처리 만족도</v>
+        <v>처리 전</v>
       </c>
       <c r="G282" t="str">
-        <v>'하자보수 처리 현황' 화면에서 처리 만족도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 처리 전이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H282" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9842,28 +9842,28 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B283" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C283" t="str">
-        <v>현장 대시보드</v>
+        <v/>
       </c>
       <c r="D283" t="str">
-        <v>OW-01</v>
+        <v/>
       </c>
       <c r="E283" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F283" t="str">
-        <v>숫자 카드 넷(진행 중 현장·이달 매출·미수금·밀린 공정)</v>
+        <v>후 사진 견주기</v>
       </c>
       <c r="G283" t="str">
-        <v>'현장 대시보드'의 숫자 카드 넷(진행 중 현장·이달 매출·미수금·밀린 공정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 후 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H283" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I283" t="str">
         <v/>
@@ -9874,7 +9874,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B284" t="str">
         <v/>
@@ -9889,10 +9889,10 @@
         <v/>
       </c>
       <c r="F284" t="str">
-        <v>기간 바꾸기와 그에 따라 다시 계산되는 숫자</v>
+        <v>원인과 무엇을 했는지 설명</v>
       </c>
       <c r="G284" t="str">
-        <v>'현장 대시보드' 화면에서 기간 바꾸기와 그에 따라 다시 계산되는 숫자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 원인과 무엇을 했는지 설명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -9921,13 +9921,13 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>오늘 해야 할 일 목록(기성 청구·자재 발주·검수 방문)</v>
+        <v>이번 처리가 보증에 들어갔는지 비용이 붙었는지</v>
       </c>
       <c r="G285" t="str">
-        <v>'현장 대시보드'의 오늘 해야 할 일 목록(기성 청구·자재 발주·검수 방문)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 이번 처리가 보증에 들어갔는지 비용이 붙었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H285" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B286" t="str">
         <v/>
@@ -9953,13 +9953,13 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v>진행 중 현장 카드 목록(주소·공정·진행률·다음 일정·밀림 표시)</v>
+        <v>처리 확인 체크와 완료 버튼</v>
       </c>
       <c r="G286" t="str">
-        <v>'현장 대시보드'의 진행 중 현장 카드 목록(주소·공정·진행률·다음 일정·밀림 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'하자보수 처리 현황'에서 처리 확인 체크와 완료 버튼을 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -9985,10 +9985,10 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>이번 주 일정 가로 띠</v>
+        <v>「다시 봐 주세요」 재접수</v>
       </c>
       <c r="G287" t="str">
-        <v>'현장 대시보드' 화면에서 이번 주 일정 가로 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 「다시 봐 주세요」 재접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H287" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B288" t="str">
         <v/>
@@ -10017,10 +10017,10 @@
         <v/>
       </c>
       <c r="F288" t="str">
-        <v>새 견적 요청 알림</v>
+        <v>처리 만족도</v>
       </c>
       <c r="G288" t="str">
-        <v>'현장 대시보드' 화면에서 새 견적 요청 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'하자보수 처리 현황' 화면에서 처리 만족도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H288" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10037,25 +10037,25 @@
         <v>SCN-030</v>
       </c>
       <c r="B289" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C289" t="str">
-        <v/>
+        <v>현장 대시보드</v>
       </c>
       <c r="D289" t="str">
-        <v/>
+        <v>OW-01</v>
       </c>
       <c r="E289" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F289" t="str">
-        <v>매출 그래프(월별)</v>
+        <v>숫자 카드 넷(진행 중 현장·이달 매출·미수금·밀린 공정)</v>
       </c>
       <c r="G289" t="str">
-        <v>'현장 대시보드' 화면에서 매출 그래프(월별)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 대시보드'의 숫자 카드 넷(진행 중 현장·이달 매출·미수금·밀린 공정)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H289" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10066,28 +10066,28 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B290" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C290" t="str">
-        <v>견적 요청함</v>
+        <v/>
       </c>
       <c r="D290" t="str">
-        <v>OW-02</v>
+        <v/>
       </c>
       <c r="E290" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F290" t="str">
-        <v>상태 탭(새 요청·확인 중·실측 잡힘·계약됨·놓침)</v>
+        <v>기간 바꾸기와 그에 따라 다시 계산되는 숫자</v>
       </c>
       <c r="G290" t="str">
-        <v>'견적 요청함'에서 상태 탭(새 요청·확인 중·실측 잡힘·계약됨·놓침)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'현장 대시보드' 화면에서 기간 바꾸기와 그에 따라 다시 계산되는 숫자가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I290" t="str">
         <v/>
@@ -10098,7 +10098,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B291" t="str">
         <v/>
@@ -10113,10 +10113,10 @@
         <v/>
       </c>
       <c r="F291" t="str">
-        <v>요청 목록(들어온 시각·평수·분야·자동 계산 금액·연락처 가림)</v>
+        <v>오늘 해야 할 일 목록(기성 청구·자재 발주·검수 방문)</v>
       </c>
       <c r="G291" t="str">
-        <v>'견적 요청함'의 요청 목록(들어온 시각·평수·분야·자동 계산 금액·연락처 가림)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'현장 대시보드'의 오늘 해야 할 일 목록(기성 청구·자재 발주·검수 방문)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H291" t="str">
         <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B292" t="str">
         <v/>
@@ -10145,13 +10145,13 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>새 요청은 표시가 다르게</v>
+        <v>진행 중 현장 카드 목록(주소·공정·진행률·다음 일정·밀림 표시)</v>
       </c>
       <c r="G292" t="str">
-        <v>'견적 요청함'의 새 요청은 표시가 다르게가 실제 데이터와 같은지 대조한다.</v>
+        <v>'현장 대시보드'의 진행 중 현장 카드 목록(주소·공정·진행률·다음 일정·밀림 표시)를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I292" t="str">
         <v/>
@@ -10162,7 +10162,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B293" t="str">
         <v/>
@@ -10177,10 +10177,10 @@
         <v/>
       </c>
       <c r="F293" t="str">
-        <v>줄을 펼치면 나오는 손님이 넣은 조건 전부</v>
+        <v>이번 주 일정 가로 띠</v>
       </c>
       <c r="G293" t="str">
-        <v>'견적 요청함' 화면에서 줄을 펼치면 나오는 손님이 넣은 조건 전부가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 대시보드' 화면에서 이번 주 일정 가로 띠가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H293" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -10209,10 +10209,10 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>담당자 배정 드롭다운</v>
+        <v>새 견적 요청 알림</v>
       </c>
       <c r="G294" t="str">
-        <v>'견적 요청함' 화면에서 담당자 배정 드롭다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 대시보드' 화면에서 새 견적 요청 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H294" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B295" t="str">
         <v/>
@@ -10241,13 +10241,13 @@
         <v/>
       </c>
       <c r="F295" t="str">
-        <v>몇 시간 안에 연락했는지 응답 시간 표시</v>
+        <v>매출 그래프(월별)</v>
       </c>
       <c r="G295" t="str">
-        <v>'견적 요청함'의 몇 시간 안에 연락했는지 응답 시간 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'현장 대시보드' 화면에서 매출 그래프(월별)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H295" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10261,25 +10261,25 @@
         <v>SCN-031</v>
       </c>
       <c r="B296" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C296" t="str">
-        <v/>
+        <v>견적 요청함</v>
       </c>
       <c r="D296" t="str">
-        <v/>
+        <v>OW-02</v>
       </c>
       <c r="E296" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F296" t="str">
-        <v>놓친 요청과 그 까닭 적기</v>
+        <v>상태 탭(새 요청·확인 중·실측 잡힘·계약됨·놓침)</v>
       </c>
       <c r="G296" t="str">
-        <v>'견적 요청함' 화면에서 놓친 요청과 그 까닭 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함'에서 상태 탭(새 요청·확인 중·실측 잡힘·계약됨·놓침)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10305,13 +10305,13 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>실측 예약으로 바로 넘기기</v>
+        <v>요청 목록(들어온 시각·평수·분야·자동 계산 금액·연락처 가림)</v>
       </c>
       <c r="G297" t="str">
-        <v>'견적 요청함' 화면에서 실측 예약으로 바로 넘기기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함'의 요청 목록(들어온 시각·평수·분야·자동 계산 금액·연락처 가림)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H297" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -10337,13 +10337,13 @@
         <v/>
       </c>
       <c r="F298" t="str">
-        <v>요청 수와 계약 성사율</v>
+        <v>새 요청은 표시가 다르게</v>
       </c>
       <c r="G298" t="str">
-        <v>'견적 요청함' 화면에서 요청 수와 계약 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함'의 새 요청은 표시가 다르게가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H298" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -10354,25 +10354,25 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B299" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C299" t="str">
-        <v>현장 상세 - 공정 편집</v>
+        <v/>
       </c>
       <c r="D299" t="str">
-        <v>OW-03</v>
+        <v/>
       </c>
       <c r="E299" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F299" t="str">
-        <v>현장 머리(주소·평수·계약금액·진행률·담당 소장)</v>
+        <v>줄을 펼치면 나오는 손님이 넣은 조건 전부</v>
       </c>
       <c r="G299" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 현장 머리(주소·평수·계약금액·진행률·담당 소장)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함' 화면에서 줄을 펼치면 나오는 손님이 넣은 조건 전부가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H299" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,13 +10401,13 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>탭(공정·자재·사진·정산)</v>
+        <v>담당자 배정 드롭다운</v>
       </c>
       <c r="G300" t="str">
-        <v>'현장 상세 - 공정 편집'에서 탭(공정·자재·사진·정산)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'견적 요청함' 화면에서 담당자 배정 드롭다운이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H300" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I300" t="str">
         <v/>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B301" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v/>
       </c>
       <c r="F301" t="str">
-        <v>공정 탭의 편집 가능한 일정표(막대를 끌어 날짜 바꾸기)</v>
+        <v>몇 시간 안에 연락했는지 응답 시간 표시</v>
       </c>
       <c r="G301" t="str">
-        <v>'현장 상세 - 공정 편집'에서 공정 탭의 편집 가능한 일정표(막대를 끌어 날짜 바꾸기)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'견적 요청함'의 몇 시간 안에 연락했는지 응답 시간 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H301" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B302" t="str">
         <v/>
@@ -10465,10 +10465,10 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>앞 공정을 밀면 뒤가 따라 밀리는 것</v>
+        <v>놓친 요청과 그 까닭 적기</v>
       </c>
       <c r="G302" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 앞 공정을 밀면 뒤가 따라 밀리는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함' 화면에서 놓친 요청과 그 까닭 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H302" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -10497,10 +10497,10 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>공정별 팀 배정과 일정 충돌 경고</v>
+        <v>실측 예약으로 바로 넘기기</v>
       </c>
       <c r="G303" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 공정별 팀 배정과 일정 충돌 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함' 화면에서 실측 예약으로 바로 넘기기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>공정 추가</v>
+        <v>요청 수와 계약 성사율</v>
       </c>
       <c r="G304" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 공정 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'견적 요청함' 화면에서 요청 수와 계약 성사율이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10549,22 +10549,22 @@
         <v>SCN-032</v>
       </c>
       <c r="B305" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C305" t="str">
-        <v/>
+        <v>현장 상세 - 공정 편집</v>
       </c>
       <c r="D305" t="str">
-        <v/>
+        <v>OW-03</v>
       </c>
       <c r="E305" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F305" t="str">
-        <v>지우기</v>
+        <v>현장 머리(주소·평수·계약금액·진행률·담당 소장)</v>
       </c>
       <c r="G305" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 현장 머리(주소·평수·계약금액·진행률·담당 소장)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H305" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10593,13 +10593,13 @@
         <v/>
       </c>
       <c r="F306" t="str">
-        <v>실제 진행률 입력</v>
+        <v>탭(공정·자재·사진·정산)</v>
       </c>
       <c r="G306" t="str">
-        <v>'현장 상세 - 공정 편집'의 실제 진행률 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'현장 상세 - 공정 편집'에서 탭(공정·자재·사진·정산)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H306" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10625,13 +10625,13 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>손님에게 보이는 것과 안 보이는 것 갈라 두기</v>
+        <v>공정 탭의 편집 가능한 일정표(막대를 끌어 날짜 바꾸기)</v>
       </c>
       <c r="G307" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 손님에게 보이는 것과 안 보이는 것 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집'에서 공정 탭의 편집 가능한 일정표(막대를 끌어 날짜 바꾸기)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H307" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I307" t="str">
         <v/>
@@ -10657,10 +10657,10 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>변경 이력</v>
+        <v>앞 공정을 밀면 뒤가 따라 밀리는 것</v>
       </c>
       <c r="G308" t="str">
-        <v>'현장 상세 - 공정 편집' 화면에서 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 앞 공정을 밀면 뒤가 따라 밀리는 것이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H308" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10674,28 +10674,28 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B309" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C309" t="str">
-        <v>자재·원가</v>
+        <v/>
       </c>
       <c r="D309" t="str">
-        <v>OW-04</v>
+        <v/>
       </c>
       <c r="E309" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F309" t="str">
-        <v>현장별 자재 목록(공정·품명·규격·수량·견적 단가·실제 단가·차액)</v>
+        <v>공정별 팀 배정과 일정 충돌 경고</v>
       </c>
       <c r="G309" t="str">
-        <v>'자재·원가'의 현장별 자재 목록(공정·품명·규격·수량·견적 단가·실제 단가·차액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 공정별 팀 배정과 일정 충돌 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I309" t="str">
         <v/>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B310" t="str">
         <v/>
@@ -10721,10 +10721,10 @@
         <v/>
       </c>
       <c r="F310" t="str">
-        <v>실제 단가를 넣으면 계산되는 차액과 마진</v>
+        <v>공정 추가</v>
       </c>
       <c r="G310" t="str">
-        <v>'자재·원가' 화면에서 실제 단가를 넣으면 계산되는 차액과 마진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 공정 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B311" t="str">
         <v/>
@@ -10753,13 +10753,13 @@
         <v/>
       </c>
       <c r="F311" t="str">
-        <v>발주 상태 배지(발주 전·발주함·입고됨·반품)</v>
+        <v>지우기</v>
       </c>
       <c r="G311" t="str">
-        <v>'자재·원가'의 발주 상태 배지(발주 전·발주함·입고됨·반품)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 지우기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I311" t="str">
         <v/>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B312" t="str">
         <v/>
@@ -10785,13 +10785,13 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>발주 안 한 것 수를 위에</v>
+        <v>실제 진행률 입력</v>
       </c>
       <c r="G312" t="str">
-        <v>'자재·원가' 화면에서 발주 안 한 것 수를 위에가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'현장 상세 - 공정 편집'의 실제 진행률 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H312" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I312" t="str">
         <v/>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B313" t="str">
         <v/>
@@ -10817,13 +10817,13 @@
         <v/>
       </c>
       <c r="F313" t="str">
-        <v>납품 예정일과 늦어지는 것 표시</v>
+        <v>손님에게 보이는 것과 안 보이는 것 갈라 두기</v>
       </c>
       <c r="G313" t="str">
-        <v>'자재·원가'의 납품 예정일과 늦어지는 것 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 손님에게 보이는 것과 안 보이는 것 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B314" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>공정별 필터</v>
+        <v>변경 이력</v>
       </c>
       <c r="G314" t="str">
-        <v>'자재·원가'에서 공정별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'현장 상세 - 공정 편집' 화면에서 변경 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H314" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10869,25 +10869,25 @@
         <v>SCN-033</v>
       </c>
       <c r="B315" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C315" t="str">
-        <v/>
+        <v>자재·원가</v>
       </c>
       <c r="D315" t="str">
-        <v/>
+        <v>OW-04</v>
       </c>
       <c r="E315" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F315" t="str">
-        <v>원가 합계와 계약금액 대비 마진율</v>
+        <v>현장별 자재 목록(공정·품명·규격·수량·견적 단가·실제 단가·차액)</v>
       </c>
       <c r="G315" t="str">
-        <v>'자재·원가'의 원가 합계와 계약금액 대비 마진율이 실제 데이터와 같은지 대조한다.</v>
+        <v>'자재·원가'의 현장별 자재 목록(공정·품명·규격·수량·견적 단가·실제 단가·차액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H315" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I315" t="str">
         <v/>
@@ -10913,10 +10913,10 @@
         <v/>
       </c>
       <c r="F316" t="str">
-        <v>자재 추가와 거래처</v>
+        <v>실제 단가를 넣으면 계산되는 차액과 마진</v>
       </c>
       <c r="G316" t="str">
-        <v>'자재·원가' 화면에서 자재 추가와 거래처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자재·원가' 화면에서 실제 단가를 넣으면 계산되는 차액과 마진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H316" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10945,13 +10945,13 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>발주서 내보내기</v>
+        <v>발주 상태 배지(발주 전·발주함·입고됨·반품)</v>
       </c>
       <c r="G317" t="str">
-        <v>'자재·원가' 화면에서 발주서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자재·원가'의 발주 상태 배지(발주 전·발주함·입고됨·반품)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H317" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I317" t="str">
         <v/>
@@ -10962,28 +10962,28 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B318" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C318" t="str">
-        <v>기성 청구·수금</v>
+        <v/>
       </c>
       <c r="D318" t="str">
-        <v>OW-05</v>
+        <v/>
       </c>
       <c r="E318" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F318" t="str">
-        <v>미수금 총액과 이달 수금액을 맨 위에</v>
+        <v>발주 안 한 것 수를 위에</v>
       </c>
       <c r="G318" t="str">
-        <v>'기성 청구·수금'의 미수금 총액과 이달 수금액을 맨 위에가 실제 데이터와 같은지 대조한다.</v>
+        <v>'자재·원가' 화면에서 발주 안 한 것 수를 위에가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H318" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I318" t="str">
         <v/>
@@ -10994,7 +10994,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B319" t="str">
         <v/>
@@ -11009,13 +11009,13 @@
         <v/>
       </c>
       <c r="F319" t="str">
-        <v>현장별</v>
+        <v>납품 예정일과 늦어지는 것 표시</v>
       </c>
       <c r="G319" t="str">
-        <v>'기성 청구·수금' 화면에서 현장별이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자재·원가'의 납품 예정일과 늦어지는 것 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H319" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I319" t="str">
         <v/>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B320" t="str">
         <v/>
@@ -11041,13 +11041,13 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v>회차별 청구 목록(계약금·착공금·중도금·잔금)</v>
+        <v>공정별 필터</v>
       </c>
       <c r="G320" t="str">
-        <v>'기성 청구·수금'의 회차별 청구 목록(계약금·착공금·중도금·잔금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'자재·원가'에서 공정별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H320" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I320" t="str">
         <v/>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B321" t="str">
         <v/>
@@ -11073,13 +11073,13 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>회차마다 예정일</v>
+        <v>원가 합계와 계약금액 대비 마진율</v>
       </c>
       <c r="G321" t="str">
-        <v>'기성 청구·수금' 화면에서 회차마다 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자재·원가'의 원가 합계와 계약금액 대비 마진율이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H321" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I321" t="str">
         <v/>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B322" t="str">
         <v/>
@@ -11105,13 +11105,13 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>금액</v>
+        <v>자재 추가와 거래처</v>
       </c>
       <c r="G322" t="str">
-        <v>'기성 청구·수금'의 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>'자재·원가' 화면에서 자재 추가와 거래처가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H322" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I322" t="str">
         <v/>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B323" t="str">
         <v/>
@@ -11137,13 +11137,13 @@
         <v/>
       </c>
       <c r="F323" t="str">
-        <v>상태(예정·청구함·수금 완료·연체)</v>
+        <v>발주서 내보내기</v>
       </c>
       <c r="G323" t="str">
-        <v>'기성 청구·수금'의 상태(예정·청구함·수금 완료·연체)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'자재·원가' 화면에서 발주서 내보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H323" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I323" t="str">
         <v/>
@@ -11157,25 +11157,25 @@
         <v>SCN-034</v>
       </c>
       <c r="B324" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C324" t="str">
-        <v/>
+        <v>기성 청구·수금</v>
       </c>
       <c r="D324" t="str">
-        <v/>
+        <v>OW-05</v>
       </c>
       <c r="E324" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F324" t="str">
-        <v>청구서 만들기와 문자로 보내기</v>
+        <v>미수금 총액과 이달 수금액을 맨 위에</v>
       </c>
       <c r="G324" t="str">
-        <v>'기성 청구·수금' 화면에서 청구서 만들기와 문자로 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금'의 미수금 총액과 이달 수금액을 맨 위에가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H324" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I324" t="str">
         <v/>
@@ -11201,10 +11201,10 @@
         <v/>
       </c>
       <c r="F325" t="str">
-        <v>입금 확인 체크</v>
+        <v>현장별</v>
       </c>
       <c r="G325" t="str">
-        <v>'기성 청구·수금' 화면에서 입금 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금' 화면에서 현장별이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H325" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11233,13 +11233,13 @@
         <v/>
       </c>
       <c r="F326" t="str">
-        <v>연체된 건 위로 올리고 며칠 늦었는지</v>
+        <v>회차별 청구 목록(계약금·착공금·중도금·잔금)</v>
       </c>
       <c r="G326" t="str">
-        <v>'기성 청구·수금' 화면에서 연체된 건 위로 올리고 며칠 늦었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금'의 회차별 청구 목록(계약금·착공금·중도금·잔금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H326" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I326" t="str">
         <v/>
@@ -11265,13 +11265,13 @@
         <v/>
       </c>
       <c r="F327" t="str">
-        <v>세금계산서 발행 상태</v>
+        <v>회차마다 예정일</v>
       </c>
       <c r="G327" t="str">
-        <v>'기성 청구·수금'의 세금계산서 발행 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'기성 청구·수금' 화면에서 회차마다 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H327" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I327" t="str">
         <v/>
@@ -11297,13 +11297,13 @@
         <v/>
       </c>
       <c r="F328" t="str">
-        <v>현장별 필터</v>
+        <v>금액</v>
       </c>
       <c r="G328" t="str">
-        <v>'기성 청구·수금'에서 현장별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기성 청구·수금'의 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H328" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I328" t="str">
         <v/>
@@ -11329,13 +11329,13 @@
         <v/>
       </c>
       <c r="F329" t="str">
-        <v>수금 예정 달력</v>
+        <v>상태(예정·청구함·수금 완료·연체)</v>
       </c>
       <c r="G329" t="str">
-        <v>'기성 청구·수금' 화면에서 수금 예정 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금'의 상태(예정·청구함·수금 완료·연체)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H329" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I329" t="str">
         <v/>
@@ -11346,25 +11346,25 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B330" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C330" t="str">
-        <v>일정 캘린더</v>
+        <v/>
       </c>
       <c r="D330" t="str">
-        <v>OW-06</v>
+        <v/>
       </c>
       <c r="E330" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F330" t="str">
-        <v>여러 현장의 일정을 한 달력에 겹쳐 보기</v>
+        <v>청구서 만들기와 문자로 보내기</v>
       </c>
       <c r="G330" t="str">
-        <v>'일정 캘린더' 화면에서 여러 현장의 일정을 한 달력에 겹쳐 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금' 화면에서 청구서 만들기와 문자로 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H330" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B331" t="str">
         <v/>
@@ -11393,13 +11393,13 @@
         <v/>
       </c>
       <c r="F331" t="str">
-        <v>현장별 색과 팀별 필터</v>
+        <v>입금 확인 체크</v>
       </c>
       <c r="G331" t="str">
-        <v>'일정 캘린더'에서 현장별 색과 팀별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기성 청구·수금' 화면에서 입금 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H331" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I331" t="str">
         <v/>
@@ -11410,7 +11410,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B332" t="str">
         <v/>
@@ -11425,10 +11425,10 @@
         <v/>
       </c>
       <c r="F332" t="str">
-        <v>일정을 끌어 다른 날로 옮기기</v>
+        <v>연체된 건 위로 올리고 며칠 늦었는지</v>
       </c>
       <c r="G332" t="str">
-        <v>'일정 캘린더' 화면에서 일정을 끌어 다른 날로 옮기기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금' 화면에서 연체된 건 위로 올리고 며칠 늦었는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H332" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B333" t="str">
         <v/>
@@ -11457,13 +11457,13 @@
         <v/>
       </c>
       <c r="F333" t="str">
-        <v>같은 팀이 두 곳에 잡히면 뜨는 겹침 경고</v>
+        <v>세금계산서 발행 상태</v>
       </c>
       <c r="G333" t="str">
-        <v>'일정 캘린더' 화면에서 같은 팀이 두 곳에 잡히면 뜨는 겹침 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금'의 세금계산서 발행 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H333" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I333" t="str">
         <v/>
@@ -11474,7 +11474,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B334" t="str">
         <v/>
@@ -11489,13 +11489,13 @@
         <v/>
       </c>
       <c r="F334" t="str">
-        <v>주 보기</v>
+        <v>현장별 필터</v>
       </c>
       <c r="G334" t="str">
-        <v>'일정 캘린더' 화면에서 주 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금'에서 현장별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H334" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I334" t="str">
         <v/>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B335" t="str">
         <v/>
@@ -11521,10 +11521,10 @@
         <v/>
       </c>
       <c r="F335" t="str">
-        <v>월 보기 전환</v>
+        <v>수금 예정 달력</v>
       </c>
       <c r="G335" t="str">
-        <v>'일정 캘린더' 화면에서 월 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기성 청구·수금' 화면에서 수금 예정 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H335" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11541,25 +11541,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B336" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C336" t="str">
-        <v/>
+        <v>일정 캘린더</v>
       </c>
       <c r="D336" t="str">
-        <v/>
+        <v>OW-06</v>
       </c>
       <c r="E336" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F336" t="str">
-        <v>날짜를 누르면 옆에 열리는 그 날 일정 목록</v>
+        <v>여러 현장의 일정을 한 달력에 겹쳐 보기</v>
       </c>
       <c r="G336" t="str">
-        <v>'일정 캘린더'의 날짜를 누르면 옆에 열리는 그 날 일정 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'일정 캘린더' 화면에서 여러 현장의 일정을 한 달력에 겹쳐 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H336" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I336" t="str">
         <v/>
@@ -11585,13 +11585,13 @@
         <v/>
       </c>
       <c r="F337" t="str">
-        <v>실측 방문</v>
+        <v>현장별 색과 팀별 필터</v>
       </c>
       <c r="G337" t="str">
-        <v>'일정 캘린더' 화면에서 실측 방문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더'에서 현장별 색과 팀별 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H337" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I337" t="str">
         <v/>
@@ -11617,10 +11617,10 @@
         <v/>
       </c>
       <c r="F338" t="str">
-        <v>검수 방문도 함께</v>
+        <v>일정을 끌어 다른 날로 옮기기</v>
       </c>
       <c r="G338" t="str">
-        <v>'일정 캘린더' 화면에서 검수 방문도 함께가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더' 화면에서 일정을 끌어 다른 날로 옮기기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H338" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11649,13 +11649,13 @@
         <v/>
       </c>
       <c r="F339" t="str">
-        <v>공휴일과 아파트 공사 금지일 표시</v>
+        <v>같은 팀이 두 곳에 잡히면 뜨는 겹침 경고</v>
       </c>
       <c r="G339" t="str">
-        <v>'일정 캘린더'의 공휴일과 아파트 공사 금지일 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'일정 캘린더' 화면에서 같은 팀이 두 곳에 잡히면 뜨는 겹침 경고가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H339" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I339" t="str">
         <v/>
@@ -11681,10 +11681,10 @@
         <v/>
       </c>
       <c r="F340" t="str">
-        <v>일정 추가</v>
+        <v>주 보기</v>
       </c>
       <c r="G340" t="str">
-        <v>'일정 캘린더' 화면에서 일정 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더' 화면에서 주 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H340" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11698,28 +11698,28 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B341" t="str">
-        <v>현장 관리</v>
+        <v/>
       </c>
       <c r="C341" t="str">
-        <v>업체 정보·직원 관리</v>
+        <v/>
       </c>
       <c r="D341" t="str">
-        <v>OW-07</v>
+        <v/>
       </c>
       <c r="E341" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F341" t="str">
-        <v>업체 기본 정보(상호·사업자번호·대표·주소·전화)와 고치기</v>
+        <v>월 보기 전환</v>
       </c>
       <c r="G341" t="str">
-        <v>'업체 정보·직원 관리'의 업체 기본 정보(상호·사업자번호·대표·주소·전화)와 고치기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'일정 캘린더' 화면에서 월 보기 전환이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H341" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I341" t="str">
         <v/>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B342" t="str">
         <v/>
@@ -11745,13 +11745,13 @@
         <v/>
       </c>
       <c r="F342" t="str">
-        <v>손님 화면에 보이는 소개 글과 대표 사진</v>
+        <v>날짜를 누르면 옆에 열리는 그 날 일정 목록</v>
       </c>
       <c r="G342" t="str">
-        <v>'업체 정보·직원 관리' 화면에서 손님 화면에 보이는 소개 글과 대표 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더'의 날짜를 누르면 옆에 열리는 그 날 일정 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H342" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I342" t="str">
         <v/>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B343" t="str">
         <v/>
@@ -11777,13 +11777,13 @@
         <v/>
       </c>
       <c r="F343" t="str">
-        <v>직원 계정 목록과 권한 3단(대표·소장·경리)</v>
+        <v>실측 방문</v>
       </c>
       <c r="G343" t="str">
-        <v>'업체 정보·직원 관리' 화면을 열고 직원 계정 목록과 권한 3단(대표·소장·경리)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'일정 캘린더' 화면에서 실측 방문이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H343" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I343" t="str">
         <v/>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B344" t="str">
         <v/>
@@ -11809,10 +11809,10 @@
         <v/>
       </c>
       <c r="F344" t="str">
-        <v>권한마다 볼 수 있는 화면 표</v>
+        <v>검수 방문도 함께</v>
       </c>
       <c r="G344" t="str">
-        <v>'업체 정보·직원 관리' 화면에서 권한마다 볼 수 있는 화면 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더' 화면에서 검수 방문도 함께가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H344" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B345" t="str">
         <v/>
@@ -11841,13 +11841,13 @@
         <v/>
       </c>
       <c r="F345" t="str">
-        <v>직원 부르기(문자 초대)</v>
+        <v>공휴일과 아파트 공사 금지일 표시</v>
       </c>
       <c r="G345" t="str">
-        <v>'업체 정보·직원 관리' 화면에서 직원 부르기(문자 초대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'일정 캘린더'의 공휴일과 아파트 공사 금지일 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H345" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I345" t="str">
         <v/>
@@ -11858,7 +11858,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B346" t="str">
         <v/>
@@ -11873,13 +11873,13 @@
         <v/>
       </c>
       <c r="F346" t="str">
-        <v>거래처 목록(자재상·인력팀·연락처·거래 조건)</v>
+        <v>일정 추가</v>
       </c>
       <c r="G346" t="str">
-        <v>'업체 정보·직원 관리'의 거래처 목록(자재상·인력팀·연락처·거래 조건)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'일정 캘린더' 화면에서 일정 추가가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H346" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I346" t="str">
         <v/>
@@ -11893,25 +11893,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B347" t="str">
-        <v/>
+        <v>현장 관리</v>
       </c>
       <c r="C347" t="str">
-        <v/>
+        <v>업체 정보·직원 관리</v>
       </c>
       <c r="D347" t="str">
-        <v/>
+        <v>OW-07</v>
       </c>
       <c r="E347" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F347" t="str">
-        <v>알림 받을 사람 고르기(견적 요청·기성 청구·하자 접수 각각)</v>
+        <v>업체 기본 정보(상호·사업자번호·대표·주소·전화)와 고치기</v>
       </c>
       <c r="G347" t="str">
-        <v>'업체 정보·직원 관리' 화면에서 알림 받을 사람 고르기(견적 요청·기성 청구·하자 접수 각각)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'업체 정보·직원 관리'의 업체 기본 정보(상호·사업자번호·대표·주소·전화)와 고치기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H347" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I347" t="str">
         <v/>
@@ -11937,10 +11937,10 @@
         <v/>
       </c>
       <c r="F348" t="str">
-        <v>사업자 서류 올리기(사업자등록증·통장사본)</v>
+        <v>손님 화면에 보이는 소개 글과 대표 사진</v>
       </c>
       <c r="G348" t="str">
-        <v>'업체 정보·직원 관리' 화면에서 사업자 서류 올리기(사업자등록증·통장사본)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'업체 정보·직원 관리' 화면에서 손님 화면에 보이는 소개 글과 대표 사진이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H348" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11969,13 +11969,13 @@
         <v/>
       </c>
       <c r="F349" t="str">
-        <v>세금계산서 기본 정보</v>
+        <v>직원 계정 목록과 권한 3단(대표·소장·경리)</v>
       </c>
       <c r="G349" t="str">
-        <v>'업체 정보·직원 관리'의 세금계산서 기본 정보가 실제 데이터와 같은지 대조한다.</v>
+        <v>'업체 정보·직원 관리' 화면을 열고 직원 계정 목록과 권한 3단(대표·소장·경리)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H349" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I349" t="str">
         <v/>
@@ -11986,28 +11986,28 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B350" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C350" t="str">
-        <v>로그인</v>
+        <v/>
       </c>
       <c r="D350" t="str">
-        <v>AU-01</v>
+        <v/>
       </c>
       <c r="E350" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F350" t="str">
-        <v>휴대폰 번호 또는 아이디와 비밀번호 입력</v>
+        <v>권한마다 볼 수 있는 화면 표</v>
       </c>
       <c r="G350" t="str">
-        <v>'로그인'의 휴대폰 번호 또는 아이디와 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'업체 정보·직원 관리' 화면에서 권한마다 볼 수 있는 화면 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H350" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I350" t="str">
         <v/>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B351" t="str">
         <v/>
@@ -12033,10 +12033,10 @@
         <v/>
       </c>
       <c r="F351" t="str">
-        <v>비밀번호 보기 눈 아이콘</v>
+        <v>직원 부르기(문자 초대)</v>
       </c>
       <c r="G351" t="str">
-        <v>'로그인' 화면에서 비밀번호 보기 눈 아이콘이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'업체 정보·직원 관리' 화면에서 직원 부르기(문자 초대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H351" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B352" t="str">
         <v/>
@@ -12065,13 +12065,13 @@
         <v/>
       </c>
       <c r="F352" t="str">
-        <v>로그인 상태 유지</v>
+        <v>거래처 목록(자재상·인력팀·연락처·거래 조건)</v>
       </c>
       <c r="G352" t="str">
-        <v>'로그인'에서 로그인 상태 유지를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'업체 정보·직원 관리'의 거래처 목록(자재상·인력팀·연락처·거래 조건)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H352" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12082,7 +12082,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B353" t="str">
         <v/>
@@ -12097,13 +12097,13 @@
         <v/>
       </c>
       <c r="F353" t="str">
-        <v>틀렸을 때 입력칸 아래에 뜨는 안내(어느 칸이 틀렸는지)</v>
+        <v>알림 받을 사람 고르기(견적 요청·기성 청구·하자 접수 각각)</v>
       </c>
       <c r="G353" t="str">
-        <v>'로그인'의 틀렸을 때 입력칸 아래에 뜨는 안내(어느 칸이 틀렸는지)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'업체 정보·직원 관리' 화면에서 알림 받을 사람 고르기(견적 요청·기성 청구·하자 접수 각각)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H353" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12114,7 +12114,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B354" t="str">
         <v/>
@@ -12129,13 +12129,13 @@
         <v/>
       </c>
       <c r="F354" t="str">
-        <v>간편 로그인 3종</v>
+        <v>사업자 서류 올리기(사업자등록증·통장사본)</v>
       </c>
       <c r="G354" t="str">
-        <v>'로그인'에서 간편 로그인 3종을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'업체 정보·직원 관리' 화면에서 사업자 서류 올리기(사업자등록증·통장사본)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H354" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I354" t="str">
         <v/>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B355" t="str">
         <v/>
@@ -12161,13 +12161,13 @@
         <v/>
       </c>
       <c r="F355" t="str">
-        <v>회원가입과 비밀번호 찾기로 가는 길</v>
+        <v>세금계산서 기본 정보</v>
       </c>
       <c r="G355" t="str">
-        <v>'로그인'에서 회원가입과 비밀번호 찾기로 가는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'업체 정보·직원 관리'의 세금계산서 기본 정보가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H355" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I355" t="str">
         <v/>
@@ -12181,25 +12181,25 @@
         <v>SCN-037</v>
       </c>
       <c r="B356" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C356" t="str">
-        <v/>
+        <v>로그인</v>
       </c>
       <c r="D356" t="str">
-        <v/>
+        <v>AU-01</v>
       </c>
       <c r="E356" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F356" t="str">
-        <v>업체 관리자로 들어가는 작은 길</v>
+        <v>휴대폰 번호 또는 아이디와 비밀번호 입력</v>
       </c>
       <c r="G356" t="str">
-        <v>'로그인' 화면에서 업체 관리자로 들어가는 작은 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'의 휴대폰 번호 또는 아이디와 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H356" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I356" t="str">
         <v/>
@@ -12225,13 +12225,13 @@
         <v/>
       </c>
       <c r="F357" t="str">
-        <v>로그인 없이 견적만 내보기</v>
+        <v>비밀번호 보기 눈 아이콘</v>
       </c>
       <c r="G357" t="str">
-        <v>'로그인'에서 로그인 없이 견적만 내보기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'로그인' 화면에서 비밀번호 보기 눈 아이콘이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H357" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I357" t="str">
         <v/>
@@ -12242,28 +12242,28 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B358" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C358" t="str">
-        <v>회원가입</v>
+        <v/>
       </c>
       <c r="D358" t="str">
-        <v>AU-02</v>
+        <v/>
       </c>
       <c r="E358" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F358" t="str">
-        <v>이름</v>
+        <v>로그인 상태 유지</v>
       </c>
       <c r="G358" t="str">
-        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'에서 로그인 상태 유지를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H358" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I358" t="str">
         <v/>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B359" t="str">
         <v/>
@@ -12289,13 +12289,13 @@
         <v/>
       </c>
       <c r="F359" t="str">
-        <v>휴대폰 번호와 인증번호 받기</v>
+        <v>틀렸을 때 입력칸 아래에 뜨는 안내(어느 칸이 틀렸는지)</v>
       </c>
       <c r="G359" t="str">
-        <v>'회원가입' 화면에서 휴대폰 번호와 인증번호 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'의 틀렸을 때 입력칸 아래에 뜨는 안내(어느 칸이 틀렸는지)에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H359" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I359" t="str">
         <v/>
@@ -12306,7 +12306,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B360" t="str">
         <v/>
@@ -12321,13 +12321,13 @@
         <v/>
       </c>
       <c r="F360" t="str">
-        <v>남은 시간과 다시 받기</v>
+        <v>간편 로그인 3종</v>
       </c>
       <c r="G360" t="str">
-        <v>'회원가입'의 남은 시간과 다시 받기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'로그인'에서 간편 로그인 3종을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H360" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I360" t="str">
         <v/>
@@ -12338,7 +12338,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B361" t="str">
         <v/>
@@ -12353,13 +12353,13 @@
         <v/>
       </c>
       <c r="F361" t="str">
-        <v>비밀번호와 조건 세 줄이 하나씩 채워지는 표시</v>
+        <v>회원가입과 비밀번호 찾기로 가는 길</v>
       </c>
       <c r="G361" t="str">
-        <v>'회원가입'의 비밀번호와 조건 세 줄이 하나씩 채워지는 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'로그인'에서 회원가입과 비밀번호 찾기로 가는 길을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H361" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I361" t="str">
         <v/>
@@ -12370,7 +12370,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B362" t="str">
         <v/>
@@ -12385,10 +12385,10 @@
         <v/>
       </c>
       <c r="F362" t="str">
-        <v>비밀번호 확인</v>
+        <v>업체 관리자로 들어가는 작은 길</v>
       </c>
       <c r="G362" t="str">
-        <v>'회원가입' 화면에서 비밀번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인' 화면에서 업체 관리자로 들어가는 작은 길이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H362" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12402,7 +12402,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>SCN-038</v>
+        <v>SCN-037</v>
       </c>
       <c r="B363" t="str">
         <v/>
@@ -12417,13 +12417,13 @@
         <v/>
       </c>
       <c r="F363" t="str">
-        <v>관심 시공 분야 고르기(선택)</v>
+        <v>로그인 없이 견적만 내보기</v>
       </c>
       <c r="G363" t="str">
-        <v>'회원가입' 화면에서 관심 시공 분야 고르기(선택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'로그인'에서 로그인 없이 견적만 내보기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H363" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I363" t="str">
         <v/>
@@ -12437,22 +12437,22 @@
         <v>SCN-038</v>
       </c>
       <c r="B364" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C364" t="str">
-        <v/>
+        <v>회원가입</v>
       </c>
       <c r="D364" t="str">
-        <v/>
+        <v>AU-02</v>
       </c>
       <c r="E364" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F364" t="str">
-        <v>약관 동의(전체 동의와 항목별)</v>
+        <v>이름</v>
       </c>
       <c r="G364" t="str">
-        <v>'회원가입' 화면에서 약관 동의(전체 동의와 항목별)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입' 화면에서 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H364" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12481,13 +12481,13 @@
         <v/>
       </c>
       <c r="F365" t="str">
-        <v>필수를 다 해야 열리는 가입 버튼</v>
+        <v>휴대폰 번호와 인증번호 받기</v>
       </c>
       <c r="G365" t="str">
-        <v>'회원가입'에서 필수를 다 해야 열리는 가입 버튼을 눌러 본다.</v>
+        <v>'회원가입' 화면에서 휴대폰 번호와 인증번호 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H365" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I365" t="str">
         <v/>
@@ -12513,13 +12513,13 @@
         <v/>
       </c>
       <c r="F366" t="str">
-        <v>이미 가입된 번호일 때 안내</v>
+        <v>남은 시간과 다시 받기</v>
       </c>
       <c r="G366" t="str">
-        <v>'회원가입' 화면에서 이미 가입된 번호일 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'회원가입'의 남은 시간과 다시 받기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H366" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I366" t="str">
         <v/>
@@ -12530,28 +12530,28 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B367" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C367" t="str">
-        <v>비밀번호 찾기</v>
+        <v/>
       </c>
       <c r="D367" t="str">
-        <v>AU-03</v>
+        <v/>
       </c>
       <c r="E367" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F367" t="str">
-        <v>찾는 방법 탭(휴대폰 인증·이메일)</v>
+        <v>비밀번호와 조건 세 줄이 하나씩 채워지는 표시</v>
       </c>
       <c r="G367" t="str">
-        <v>'비밀번호 찾기'에서 찾는 방법 탭(휴대폰 인증·이메일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'회원가입'의 비밀번호와 조건 세 줄이 하나씩 채워지는 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H367" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I367" t="str">
         <v/>
@@ -12562,7 +12562,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B368" t="str">
         <v/>
@@ -12577,13 +12577,13 @@
         <v/>
       </c>
       <c r="F368" t="str">
-        <v>방법별 입력칸</v>
+        <v>비밀번호 확인</v>
       </c>
       <c r="G368" t="str">
-        <v>'비밀번호 찾기'의 방법별 입력칸에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'회원가입' 화면에서 비밀번호 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H368" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I368" t="str">
         <v/>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B369" t="str">
         <v/>
@@ -12609,13 +12609,13 @@
         <v/>
       </c>
       <c r="F369" t="str">
-        <v>인증번호 받기와 남은 시간</v>
+        <v>관심 시공 분야 고르기(선택)</v>
       </c>
       <c r="G369" t="str">
-        <v>'비밀번호 찾기'의 인증번호 받기와 남은 시간이 실제 데이터와 같은지 대조한다.</v>
+        <v>'회원가입' 화면에서 관심 시공 분야 고르기(선택)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H369" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I369" t="str">
         <v/>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B370" t="str">
         <v/>
@@ -12641,13 +12641,13 @@
         <v/>
       </c>
       <c r="F370" t="str">
-        <v>인증이 끝나면 나오는 새 비밀번호 입력</v>
+        <v>약관 동의(전체 동의와 항목별)</v>
       </c>
       <c r="G370" t="str">
-        <v>'비밀번호 찾기'의 인증이 끝나면 나오는 새 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'회원가입' 화면에서 약관 동의(전체 동의와 항목별)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H370" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I370" t="str">
         <v/>
@@ -12658,7 +12658,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B371" t="str">
         <v/>
@@ -12673,13 +12673,13 @@
         <v/>
       </c>
       <c r="F371" t="str">
-        <v>조건 세 줄 표시</v>
+        <v>필수를 다 해야 열리는 가입 버튼</v>
       </c>
       <c r="G371" t="str">
-        <v>'비밀번호 찾기'의 조건 세 줄 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'회원가입'에서 필수를 다 해야 열리는 가입 버튼을 눌러 본다.</v>
       </c>
       <c r="H371" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I371" t="str">
         <v/>
@@ -12690,7 +12690,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>SCN-039</v>
+        <v>SCN-038</v>
       </c>
       <c r="B372" t="str">
         <v/>
@@ -12705,13 +12705,13 @@
         <v/>
       </c>
       <c r="F372" t="str">
-        <v>바꾸고 나면 바로 로그인으로</v>
+        <v>이미 가입된 번호일 때 안내</v>
       </c>
       <c r="G372" t="str">
-        <v>'비밀번호 찾기'에서 바꾸고 나면 바로 로그인으로를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'회원가입' 화면에서 이미 가입된 번호일 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H372" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I372" t="str">
         <v/>
@@ -12725,25 +12725,25 @@
         <v>SCN-039</v>
       </c>
       <c r="B373" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C373" t="str">
-        <v/>
+        <v>비밀번호 찾기</v>
       </c>
       <c r="D373" t="str">
-        <v/>
+        <v>AU-03</v>
       </c>
       <c r="E373" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F373" t="str">
-        <v>가입한 적 없는 번호일 때 안내</v>
+        <v>찾는 방법 탭(휴대폰 인증·이메일)</v>
       </c>
       <c r="G373" t="str">
-        <v>'비밀번호 찾기' 화면에서 가입한 적 없는 번호일 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기'에서 찾는 방법 탭(휴대폰 인증·이메일)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H373" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I373" t="str">
         <v/>
@@ -12769,13 +12769,13 @@
         <v/>
       </c>
       <c r="F374" t="str">
-        <v>그래도 안 되면 전화 상담</v>
+        <v>방법별 입력칸</v>
       </c>
       <c r="G374" t="str">
-        <v>'비밀번호 찾기' 화면에서 그래도 안 되면 전화 상담이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기'의 방법별 입력칸에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H374" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I374" t="str">
         <v/>
@@ -12786,28 +12786,28 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B375" t="str">
-        <v>계정</v>
+        <v/>
       </c>
       <c r="C375" t="str">
-        <v>내 정보</v>
+        <v/>
       </c>
       <c r="D375" t="str">
-        <v>AU-04</v>
+        <v/>
       </c>
       <c r="E375" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F375" t="str">
-        <v>프로필 사진과 이름</v>
+        <v>인증번호 받기와 남은 시간</v>
       </c>
       <c r="G375" t="str">
-        <v>'내 정보' 화면에서 프로필 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기'의 인증번호 받기와 남은 시간이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H375" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I375" t="str">
         <v/>
@@ -12818,7 +12818,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B376" t="str">
         <v/>
@@ -12833,13 +12833,13 @@
         <v/>
       </c>
       <c r="F376" t="str">
-        <v>연락처 고치기</v>
+        <v>인증이 끝나면 나오는 새 비밀번호 입력</v>
       </c>
       <c r="G376" t="str">
-        <v>'내 정보' 화면에서 연락처 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기'의 인증이 끝나면 나오는 새 비밀번호 입력에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H376" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I376" t="str">
         <v/>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B377" t="str">
         <v/>
@@ -12865,13 +12865,13 @@
         <v/>
       </c>
       <c r="F377" t="str">
-        <v>내 현장 목록(진행 중·끝남)과 각각으로 가는 길</v>
+        <v>조건 세 줄 표시</v>
       </c>
       <c r="G377" t="str">
-        <v>'내 정보'의 내 현장 목록(진행 중·끝남)과 각각으로 가는 길을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'비밀번호 찾기'의 조건 세 줄 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H377" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I377" t="str">
         <v/>
@@ -12882,7 +12882,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B378" t="str">
         <v/>
@@ -12897,13 +12897,13 @@
         <v/>
       </c>
       <c r="F378" t="str">
-        <v>저장한 견적 목록</v>
+        <v>바꾸고 나면 바로 로그인으로</v>
       </c>
       <c r="G378" t="str">
-        <v>'내 정보'의 저장한 견적 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'비밀번호 찾기'에서 바꾸고 나면 바로 로그인으로를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H378" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I378" t="str">
         <v/>
@@ -12914,7 +12914,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B379" t="str">
         <v/>
@@ -12929,10 +12929,10 @@
         <v/>
       </c>
       <c r="F379" t="str">
-        <v>관심 시공 분야 칩 고치기</v>
+        <v>가입한 적 없는 번호일 때 안내</v>
       </c>
       <c r="G379" t="str">
-        <v>'내 정보' 화면에서 관심 시공 분야 칩 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기' 화면에서 가입한 적 없는 번호일 때 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H379" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>SCN-040</v>
+        <v>SCN-039</v>
       </c>
       <c r="B380" t="str">
         <v/>
@@ -12961,10 +12961,10 @@
         <v/>
       </c>
       <c r="F380" t="str">
-        <v>알림 설정 스위치(공사 진행·추가공사·청구·하자보수)</v>
+        <v>그래도 안 되면 전화 상담</v>
       </c>
       <c r="G380" t="str">
-        <v>'내 정보' 화면에서 알림 설정 스위치(공사 진행·추가공사·청구·하자보수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'비밀번호 찾기' 화면에서 그래도 안 되면 전화 상담이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H380" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12981,22 +12981,22 @@
         <v>SCN-040</v>
       </c>
       <c r="B381" t="str">
-        <v/>
+        <v>계정</v>
       </c>
       <c r="C381" t="str">
-        <v/>
+        <v>내 정보</v>
       </c>
       <c r="D381" t="str">
-        <v/>
+        <v>AU-04</v>
       </c>
       <c r="E381" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F381" t="str">
-        <v>알림 받을 방법(문자·카톡·앱)</v>
+        <v>프로필 사진과 이름</v>
       </c>
       <c r="G381" t="str">
-        <v>'내 정보' 화면에서 알림 받을 방법(문자·카톡·앱)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보' 화면에서 프로필 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H381" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -13025,10 +13025,10 @@
         <v/>
       </c>
       <c r="F382" t="str">
-        <v>비밀번호 바꾸기</v>
+        <v>연락처 고치기</v>
       </c>
       <c r="G382" t="str">
-        <v>'내 정보' 화면에서 비밀번호 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 정보' 화면에서 연락처 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H382" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -13057,24 +13057,216 @@
         <v/>
       </c>
       <c r="F383" t="str">
+        <v>내 현장 목록(진행 중·끝남)과 각각으로 가는 길</v>
+      </c>
+      <c r="G383" t="str">
+        <v>'내 정보'의 내 현장 목록(진행 중·끝남)과 각각으로 가는 길을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+      </c>
+      <c r="H383" t="str">
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+      </c>
+      <c r="I383" t="str">
+        <v/>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B384" t="str">
+        <v/>
+      </c>
+      <c r="C384" t="str">
+        <v/>
+      </c>
+      <c r="D384" t="str">
+        <v/>
+      </c>
+      <c r="E384" t="str">
+        <v/>
+      </c>
+      <c r="F384" t="str">
+        <v>저장한 견적 목록</v>
+      </c>
+      <c r="G384" t="str">
+        <v>'내 정보'의 저장한 견적 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+      </c>
+      <c r="H384" t="str">
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+      </c>
+      <c r="I384" t="str">
+        <v/>
+      </c>
+      <c r="J384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B385" t="str">
+        <v/>
+      </c>
+      <c r="C385" t="str">
+        <v/>
+      </c>
+      <c r="D385" t="str">
+        <v/>
+      </c>
+      <c r="E385" t="str">
+        <v/>
+      </c>
+      <c r="F385" t="str">
+        <v>관심 시공 분야 칩 고치기</v>
+      </c>
+      <c r="G385" t="str">
+        <v>'내 정보' 화면에서 관심 시공 분야 칩 고치기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H385" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I385" t="str">
+        <v/>
+      </c>
+      <c r="J385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B386" t="str">
+        <v/>
+      </c>
+      <c r="C386" t="str">
+        <v/>
+      </c>
+      <c r="D386" t="str">
+        <v/>
+      </c>
+      <c r="E386" t="str">
+        <v/>
+      </c>
+      <c r="F386" t="str">
+        <v>알림 설정 스위치(공사 진행·추가공사·청구·하자보수)</v>
+      </c>
+      <c r="G386" t="str">
+        <v>'내 정보' 화면에서 알림 설정 스위치(공사 진행·추가공사·청구·하자보수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H386" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I386" t="str">
+        <v/>
+      </c>
+      <c r="J386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B387" t="str">
+        <v/>
+      </c>
+      <c r="C387" t="str">
+        <v/>
+      </c>
+      <c r="D387" t="str">
+        <v/>
+      </c>
+      <c r="E387" t="str">
+        <v/>
+      </c>
+      <c r="F387" t="str">
+        <v>알림 받을 방법(문자·카톡·앱)</v>
+      </c>
+      <c r="G387" t="str">
+        <v>'내 정보' 화면에서 알림 받을 방법(문자·카톡·앱)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H387" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I387" t="str">
+        <v/>
+      </c>
+      <c r="J387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B388" t="str">
+        <v/>
+      </c>
+      <c r="C388" t="str">
+        <v/>
+      </c>
+      <c r="D388" t="str">
+        <v/>
+      </c>
+      <c r="E388" t="str">
+        <v/>
+      </c>
+      <c r="F388" t="str">
+        <v>비밀번호 바꾸기</v>
+      </c>
+      <c r="G388" t="str">
+        <v>'내 정보' 화면에서 비밀번호 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H388" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I388" t="str">
+        <v/>
+      </c>
+      <c r="J388" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>SCN-040</v>
+      </c>
+      <c r="B389" t="str">
+        <v/>
+      </c>
+      <c r="C389" t="str">
+        <v/>
+      </c>
+      <c r="D389" t="str">
+        <v/>
+      </c>
+      <c r="E389" t="str">
+        <v/>
+      </c>
+      <c r="F389" t="str">
         <v>회원 탈퇴와 그 전에 알려 줄 것(보증 기간이 남았다는 것)</v>
       </c>
-      <c r="G383" t="str">
+      <c r="G389" t="str">
         <v>'내 정보' 화면에서 회원 탈퇴와 그 전에 알려 줄 것(보증 기간이 남았다는 것)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
-      <c r="H383" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
-      </c>
-      <c r="I383" t="str">
-        <v/>
-      </c>
-      <c r="J383" t="str">
+      <c r="H389" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I389" t="str">
+        <v/>
+      </c>
+      <c r="J389" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J383"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J389"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
@@ -1412,10 +1412,10 @@
         <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>브라우저 폭을 390px 로 좁혀 화면을 훑고, 360px 로 한 번 더 훑는다. ⚠ 세로 flex 로 바꾼 상자의 자식이 밀리는 것은 390px 에서는 안 보이고 360px 에서만 나온다.</v>
       </c>
       <c r="H19" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>두 폭 모두에서 가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/인테리어_디럭스/08_검수시나리오.xlsx
@@ -1572,7 +1572,7 @@
         <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
+        <v>스펙팩 7-9 의 글을 화면에 붙여 넣으면 ⑧번이 잰다(7-9-2 는 파일만 보므로 대비를 재지 않는다). ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
         <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
